--- a/tests/templ_versions/043_simple_valid.xlsx
+++ b/tests/templ_versions/043_simple_valid.xlsx
@@ -8,17 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dlinke\MyProg_local\gh-nfdi4cat\voc4cat-tool\tests\templ_versions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ED10178-C778-4335-9997-B87658F5F012}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D362BA8-3A2A-4F04-BF41-7D6237139B4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5205" yWindow="4455" windowWidth="28800" windowHeight="15825" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Introduction" sheetId="1" r:id="rId1"/>
-    <sheet name="Concept Scheme" sheetId="3" r:id="rId2"/>
-    <sheet name="Concepts" sheetId="4" r:id="rId3"/>
-    <sheet name="Additional Concept Features" sheetId="5" r:id="rId4"/>
-    <sheet name="Collections" sheetId="6" r:id="rId5"/>
-    <sheet name="Prefix Sheet" sheetId="7" r:id="rId6"/>
+    <sheet name="Concept Scheme" sheetId="3" r:id="rId1"/>
+    <sheet name="Concepts" sheetId="4" r:id="rId2"/>
+    <sheet name="Additional Concept Features" sheetId="5" r:id="rId3"/>
+    <sheet name="Collections" sheetId="6" r:id="rId4"/>
+    <sheet name="Prefix Sheet" sheetId="7" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -138,19 +137,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="111">
-  <si>
-    <t>SKOS Vocabulary Template</t>
-  </si>
-  <si>
-    <t>Version:</t>
-  </si>
-  <si>
-    <t>0.4.3</t>
-  </si>
-  <si>
-    <t>Please refer to the example template for example implementation</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="107">
   <si>
     <t>Concept Scheme</t>
   </si>
@@ -309,39 +296,6 @@
   </si>
   <si>
     <t>http://example.com/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Purpose: This spreadsheet is a template for information that can be converted into SKOS RDF data. This template utilises SKOS model elements. For further information for how to use this spreadsheet, please read https://www.w3.org/TR/skos-reference/ and https://www.w3.org/TR/skos-primer/ </t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Validate your data here: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>https://vocexcel.surroundaustralia.com/</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">For VocPub specifications, see: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>https://surroundaustralia.github.io/vocpub-profile/specification.html</t>
-    </r>
   </si>
   <si>
     <t>CGI</t>
@@ -497,13 +451,22 @@
   </si>
   <si>
     <t>Parent IRIs</t>
+  </si>
+  <si>
+    <t>Template Version</t>
+  </si>
+  <si>
+    <t>0.4.3, rev. 2025-07a</t>
+  </si>
+  <si>
+    <t>Version of the xlsx template</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -564,13 +527,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF1155CC"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="9"/>
       <color rgb="FF000000"/>
@@ -597,24 +553,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8E7CC3"/>
-        <bgColor rgb="FF8E7CC3"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor theme="0"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -641,33 +585,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -679,37 +611,31 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -722,31 +648,12 @@
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="1">
     <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFD9EAD3"/>
           <bgColor rgb="FFD9EAD3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFB47CFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9EAD3"/>
-          <bgColor rgb="FFD9EAD3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFB7E1CD"/>
-          <bgColor rgb="FFB7E1CD"/>
         </patternFill>
       </fill>
     </dxf>
@@ -960,1546 +867,1179 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
-  <dimension ref="A1:J28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5546875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A1" s="7"/>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
-      <c r="I1" s="8"/>
-      <c r="J1" s="8"/>
-    </row>
-    <row r="2" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A2" s="8"/>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8"/>
-    </row>
-    <row r="3" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A3" s="8"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8"/>
-      <c r="J3" s="8"/>
-    </row>
-    <row r="4" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="8"/>
-    </row>
-    <row r="5" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8"/>
-      <c r="J5" s="8"/>
-    </row>
-    <row r="6" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
-      <c r="J6" s="8"/>
-    </row>
-    <row r="7" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="I7" s="21"/>
-      <c r="J7" s="21"/>
-    </row>
-    <row r="8" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="9"/>
-      <c r="J8" s="9"/>
-    </row>
-    <row r="9" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9"/>
-    </row>
-    <row r="10" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="9"/>
-    </row>
-    <row r="11" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="J11" s="8" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
-    </row>
-    <row r="13" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="8"/>
-      <c r="J13" s="8"/>
-    </row>
-    <row r="14" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A14" s="8"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
-      <c r="H14" s="8"/>
-      <c r="I14" s="8"/>
-      <c r="J14" s="8"/>
-    </row>
-    <row r="15" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A15" s="8"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="8"/>
-      <c r="J15" s="8"/>
-    </row>
-    <row r="16" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A16" s="8"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="8"/>
-      <c r="H16" s="8"/>
-      <c r="I16" s="8"/>
-      <c r="J16" s="8"/>
-    </row>
-    <row r="17" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A17" s="8"/>
-      <c r="B17" s="21" t="s">
-        <v>57</v>
-      </c>
-      <c r="C17" s="21"/>
-      <c r="D17" s="21"/>
-      <c r="E17" s="21"/>
-      <c r="F17" s="21"/>
-      <c r="G17" s="21"/>
-      <c r="H17" s="8"/>
-      <c r="I17" s="8"/>
-      <c r="J17" s="8"/>
-    </row>
-    <row r="18" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A18" s="8"/>
-      <c r="B18" s="21"/>
-      <c r="C18" s="21"/>
-      <c r="D18" s="21"/>
-      <c r="E18" s="21"/>
-      <c r="F18" s="21"/>
-      <c r="G18" s="21"/>
-      <c r="H18" s="8"/>
-      <c r="I18" s="8"/>
-      <c r="J18" s="8"/>
-    </row>
-    <row r="19" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A19" s="8"/>
-      <c r="B19" s="21"/>
-      <c r="C19" s="21"/>
-      <c r="D19" s="21"/>
-      <c r="E19" s="21"/>
-      <c r="F19" s="21"/>
-      <c r="G19" s="21"/>
-      <c r="H19" s="8"/>
-      <c r="I19" s="8"/>
-      <c r="J19" s="8"/>
-    </row>
-    <row r="20" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A20" s="8"/>
-      <c r="B20" s="21"/>
-      <c r="C20" s="21"/>
-      <c r="D20" s="21"/>
-      <c r="E20" s="21"/>
-      <c r="F20" s="21"/>
-      <c r="G20" s="21"/>
-      <c r="H20" s="8"/>
-      <c r="I20" s="8"/>
-      <c r="J20" s="8"/>
-    </row>
-    <row r="21" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A21" s="8"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="8"/>
-      <c r="G21" s="8"/>
-      <c r="H21" s="8"/>
-      <c r="I21" s="8"/>
-      <c r="J21" s="8"/>
-    </row>
-    <row r="22" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A22" s="8"/>
-      <c r="B22" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="C22" s="21"/>
-      <c r="D22" s="21"/>
-      <c r="E22" s="21"/>
-      <c r="F22" s="21"/>
-      <c r="G22" s="21"/>
-      <c r="H22" s="8"/>
-      <c r="I22" s="8"/>
-      <c r="J22" s="8"/>
-    </row>
-    <row r="23" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A23" s="8"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="8"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="8"/>
-      <c r="G23" s="8"/>
-      <c r="H23" s="8"/>
-      <c r="I23" s="8"/>
-      <c r="J23" s="8"/>
-    </row>
-    <row r="24" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A24" s="8"/>
-      <c r="B24" s="21" t="s">
-        <v>58</v>
-      </c>
-      <c r="C24" s="21"/>
-      <c r="D24" s="21"/>
-      <c r="E24" s="21"/>
-      <c r="F24" s="21"/>
-      <c r="G24" s="21"/>
-      <c r="H24" s="8"/>
-      <c r="I24" s="8"/>
-      <c r="J24" s="8"/>
-    </row>
-    <row r="25" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A25" s="8"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
-      <c r="G25" s="8"/>
-      <c r="H25" s="8"/>
-      <c r="I25" s="8"/>
-      <c r="J25" s="8"/>
-    </row>
-    <row r="26" spans="1:10" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="6"/>
-      <c r="B26" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="C26" s="21"/>
-      <c r="D26" s="21"/>
-      <c r="E26" s="21"/>
-      <c r="F26" s="21"/>
-      <c r="G26" s="21"/>
-      <c r="H26" s="6"/>
-      <c r="I26" s="6"/>
-      <c r="J26" s="6"/>
-    </row>
-    <row r="27" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A27" s="8"/>
-      <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="9"/>
-      <c r="H27" s="8"/>
-      <c r="I27" s="8"/>
-      <c r="J27" s="8"/>
-    </row>
-    <row r="28" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A28" s="8"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="8"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="8"/>
-      <c r="G28" s="8"/>
-      <c r="H28" s="8"/>
-      <c r="I28" s="8"/>
-      <c r="J28" s="8"/>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="B24:G24"/>
-    <mergeCell ref="B26:G26"/>
-    <mergeCell ref="H7:J7"/>
-    <mergeCell ref="B17:G20"/>
-    <mergeCell ref="B22:G22"/>
-  </mergeCells>
-  <conditionalFormatting sqref="A1:J2">
-    <cfRule type="notContainsBlanks" dxfId="2" priority="2">
-      <formula>LEN(TRIM(A1))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H1:J10 A1:G28 H12:J28">
-    <cfRule type="containsBlanks" dxfId="1" priority="1">
-      <formula>LEN(TRIM(A1))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:D999"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5546875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14.44140625" customWidth="1"/>
-    <col min="2" max="2" width="64.109375" customWidth="1"/>
-    <col min="3" max="3" width="32.33203125" customWidth="1"/>
+    <col min="1" max="1" width="14.42578125" customWidth="1"/>
+    <col min="2" max="2" width="64.140625" customWidth="1"/>
+    <col min="3" max="3" width="32.28515625" customWidth="1"/>
     <col min="4" max="4" width="29" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+    <row r="1" spans="1:4" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+    </row>
+    <row r="2" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-    </row>
-    <row r="2" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="B3" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="C2" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="3" t="s">
+    </row>
+    <row r="4" spans="1:4" ht="36" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="B4" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="C3" s="3" t="s">
+      <c r="D4" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="B5" s="14">
+        <v>40008</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="D5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="19" t="s">
-        <v>109</v>
-      </c>
-      <c r="C4" s="3" t="s">
+    </row>
+    <row r="6" spans="1:4" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+      <c r="B6" s="14">
+        <v>44005</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="18">
-        <v>40008</v>
-      </c>
-      <c r="C5" s="3" t="s">
+      <c r="D6" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="B7" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+      <c r="D7" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="18">
-        <v>44005</v>
-      </c>
-      <c r="C6" s="3" t="s">
+    </row>
+    <row r="8" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="B8" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+      <c r="D8" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="C7" s="3" t="s">
+      <c r="B9" s="13">
+        <v>2016.01</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
+    <row r="10" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+      <c r="B10" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="17">
-        <v>2016.01</v>
-      </c>
-      <c r="C9" s="3" t="s">
+      <c r="D10" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="B11" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+      <c r="D11" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="17" t="s">
-        <v>63</v>
-      </c>
-      <c r="C10" s="3" t="s">
+    </row>
+    <row r="12" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
+      <c r="B12" s="9"/>
+      <c r="C12" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B11" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B12" s="13"/>
-      <c r="C12" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="D12" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:4" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="15" spans="1:4" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="1:4" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="17" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="18" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="19" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="20" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="21" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="22" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="23" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="24" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="25" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="26" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="27" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="28" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="29" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="30" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="31" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="32" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="33" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="34" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="35" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="36" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="37" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="38" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="39" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="40" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="41" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="42" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="43" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="44" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="45" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="46" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="47" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="48" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="49" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="50" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="51" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="52" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="53" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="54" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="55" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="56" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="57" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="58" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="59" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="60" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="61" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="62" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="63" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="64" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="65" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="66" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="67" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="68" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="69" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="70" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="71" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="72" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="73" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="74" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="75" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="76" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="77" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="78" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="79" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="80" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="81" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="82" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="83" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="84" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="85" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="86" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="87" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="88" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="89" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="90" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="91" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="92" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="93" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="94" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="95" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="96" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="97" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="98" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="99" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="100" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="101" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="102" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="103" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="104" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="105" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="106" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="107" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="108" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="109" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="110" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="111" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="112" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="113" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="114" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="115" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="116" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="117" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="118" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="119" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="120" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="121" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="122" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="123" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="124" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="125" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="126" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="127" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="128" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="129" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="130" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="131" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="132" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="133" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="134" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="135" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="136" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="137" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="138" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="139" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="140" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="141" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="142" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="143" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="144" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="145" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="146" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="147" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="148" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="149" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="150" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="151" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="152" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="153" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="154" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="155" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="156" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="157" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="158" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="159" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="160" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="161" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="162" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="163" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="164" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="165" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="166" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="167" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="168" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="169" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="170" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="171" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="172" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="173" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="174" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="175" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="176" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="177" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="178" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="179" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="180" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="181" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="182" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="183" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="184" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="185" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="186" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="187" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="188" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="189" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="190" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="191" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="192" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="193" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="194" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="195" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="196" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="197" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="198" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="199" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="200" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="201" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="202" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="203" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="204" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="205" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="206" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="207" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="208" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="209" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="210" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="211" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="212" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="213" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="214" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="215" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="216" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="217" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="218" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="219" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="220" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="221" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="222" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="223" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="224" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="225" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="226" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="227" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="228" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="229" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="230" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="231" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="232" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="233" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="234" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="235" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="236" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="237" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="238" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="239" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="240" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="241" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="242" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="243" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="244" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="245" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="246" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="247" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="248" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="249" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="250" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="251" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="252" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="253" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="254" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="255" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="256" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="257" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="258" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="259" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="260" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="261" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="262" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="263" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="264" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="265" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="266" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="267" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="268" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="269" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="270" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="271" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="272" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="273" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="274" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="275" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="276" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="277" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="278" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="279" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="280" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="281" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="282" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="283" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="284" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="285" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="286" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="287" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="288" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="289" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="290" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="291" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="292" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="293" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="294" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="295" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="296" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="297" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="298" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="299" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="300" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="301" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="302" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="303" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="304" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="305" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="306" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="307" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="308" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="309" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="310" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="311" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="312" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="313" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="314" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="315" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="316" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="317" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="318" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="319" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="320" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="321" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="322" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="323" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="324" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="325" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="326" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="327" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="328" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="329" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="330" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="331" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="332" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="333" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="334" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="335" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="336" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="337" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="338" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="339" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="340" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="341" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="342" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="343" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="344" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="345" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="346" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="347" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="348" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="349" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="350" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="351" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="352" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="353" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="354" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="355" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="356" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="357" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="358" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="359" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="360" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="361" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="362" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="363" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="364" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="365" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="366" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="367" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="368" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="369" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="370" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="371" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="372" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="373" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="374" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="375" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="376" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="377" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="378" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="379" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="380" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="381" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="382" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="383" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="384" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="385" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="386" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="387" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="388" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="389" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="390" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="391" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="392" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="393" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="394" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="395" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="396" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="397" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="398" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="399" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="400" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="401" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="402" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="403" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="404" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="405" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="406" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="407" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="408" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="409" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="410" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="411" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="412" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="413" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="414" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="415" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="416" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="417" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="418" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="419" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="420" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="421" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="422" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="423" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="424" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="425" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="426" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="427" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="428" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="429" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="430" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="431" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="432" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="433" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="434" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="435" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="436" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="437" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="438" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="439" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="440" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="441" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="442" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="443" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="444" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="445" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="446" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="447" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="448" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="449" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="450" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="451" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="452" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="453" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="454" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="455" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="456" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="457" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="458" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="459" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="460" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="461" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="462" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="463" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="464" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="465" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="466" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="467" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="468" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="469" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="470" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="471" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="472" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="473" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="474" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="475" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="476" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="477" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="478" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="479" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="480" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="481" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="482" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="483" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="484" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="485" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="486" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="487" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="488" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="489" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="490" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="491" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="492" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="493" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="494" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="495" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="496" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="497" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="498" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="499" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="500" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="501" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="502" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="503" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="504" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="505" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="506" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="507" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="508" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="509" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="510" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="511" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="512" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="513" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="514" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="515" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="516" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="517" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="518" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="519" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="520" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="521" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="522" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="523" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="524" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="525" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="526" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="527" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="528" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="529" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="530" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="531" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="532" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="533" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="534" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="535" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="536" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="537" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="538" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="539" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="540" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="541" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="542" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="543" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="544" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="545" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="546" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="547" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="548" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="549" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="550" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="551" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="552" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="553" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="554" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="555" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="556" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="557" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="558" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="559" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="560" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="561" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="562" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="563" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="564" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="565" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="566" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="567" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="568" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="569" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="570" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="571" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="572" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="573" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="574" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="575" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="576" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="577" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="578" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="579" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="580" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="581" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="582" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="583" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="584" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="585" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="586" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="587" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="588" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="589" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="590" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="591" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="592" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="593" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="594" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="595" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="596" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="597" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="598" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="599" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="600" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="601" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="602" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="603" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="604" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="605" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="606" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="607" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="608" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="609" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="610" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="611" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="612" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="613" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="614" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="615" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="616" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="617" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="618" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="619" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="620" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="621" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="622" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="623" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="624" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="625" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="626" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="627" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="628" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="629" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="630" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="631" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="632" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="633" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="634" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="635" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="636" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="637" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="638" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="639" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="640" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="641" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="642" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="643" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="644" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="645" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="646" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="647" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="648" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="649" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="650" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="651" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="652" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="653" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="654" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="655" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="656" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="657" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="658" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="659" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="660" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="661" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="662" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="663" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="664" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="665" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="666" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="667" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="668" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="669" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="670" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="671" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="672" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="673" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="674" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="675" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="676" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="677" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="678" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="679" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="680" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="681" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="682" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="683" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="684" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="685" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="686" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="687" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="688" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="689" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="690" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="691" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="692" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="693" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="694" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="695" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="696" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="697" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="698" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="699" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="700" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="701" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="702" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="703" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="704" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="705" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="706" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="707" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="708" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="709" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="710" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="711" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="712" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="713" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="714" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="715" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="716" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="717" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="718" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="719" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="720" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="721" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="722" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="723" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="724" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="725" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="726" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="727" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="728" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="729" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="730" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="731" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="732" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="733" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="734" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="735" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="736" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="737" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="738" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="739" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="740" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="741" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="742" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="743" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="744" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="745" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="746" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="747" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="748" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="749" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="750" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="751" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="752" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="753" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="754" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="755" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="756" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="757" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="758" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="759" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="760" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="761" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="762" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="763" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="764" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="765" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="766" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="767" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="768" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="769" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="770" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="771" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="772" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="773" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="774" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="775" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="776" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="777" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="778" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="779" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="780" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="781" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="782" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="783" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="784" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="785" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="786" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="787" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="788" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="789" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="790" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="791" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="792" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="793" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="794" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="795" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="796" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="797" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="798" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="799" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="800" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="801" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="802" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="803" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="804" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="805" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="806" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="807" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="808" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="809" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="810" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="811" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="812" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="813" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="814" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="815" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="816" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="817" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="818" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="819" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="820" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="821" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="822" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="823" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="824" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="825" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="826" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="827" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="828" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="829" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="830" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="831" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="832" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="833" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="834" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="835" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="836" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="837" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="838" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="839" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="840" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="841" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="842" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="843" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="844" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="845" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="846" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="847" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="848" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="849" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="850" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="851" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="852" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="853" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="854" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="855" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="856" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="857" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="858" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="859" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="860" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="861" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="862" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="863" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="864" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="865" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="866" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="867" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="868" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="869" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="870" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="871" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="872" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="873" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="874" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="875" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="876" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="877" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="878" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="879" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="880" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="881" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="882" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="883" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="884" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="885" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="886" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="887" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="888" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="889" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="890" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="891" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="892" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="893" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="894" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="895" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="896" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="897" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="898" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="899" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="900" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="901" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="902" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="903" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="904" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="905" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="906" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="907" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="908" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="909" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="910" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="911" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="912" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="913" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="914" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="915" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="916" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="917" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="918" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="919" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="920" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="921" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="922" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="923" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="924" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="925" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="926" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="927" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="928" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="929" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="930" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="931" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="932" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="933" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="934" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="935" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="936" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="937" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="938" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="939" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="940" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="941" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="942" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="943" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="944" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="945" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="946" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="947" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="948" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="949" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="950" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="951" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="952" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="953" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="954" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="955" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="956" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="957" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="958" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="959" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="960" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="961" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="962" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="963" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="964" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="965" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="966" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="967" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="968" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="969" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="970" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="971" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="972" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="973" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="974" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="975" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="976" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="977" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="978" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="979" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="980" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="981" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="982" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="983" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="984" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="985" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="986" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="987" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="988" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="989" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="990" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="991" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="992" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="993" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="994" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="995" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="996" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="997" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="998" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="999" ht="13.2" x14ac:dyDescent="0.25"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="15" spans="1:4" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="16" spans="1:4" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="17" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="18" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="19" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="20" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="21" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="22" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="23" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="24" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="25" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="26" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="27" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="28" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="29" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="30" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="31" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="32" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="33" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="34" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="35" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="36" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="37" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="38" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="39" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="40" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="41" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="42" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="43" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="44" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="45" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="46" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="47" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="48" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="49" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="50" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="51" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="52" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="53" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="54" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="55" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="56" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="57" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="58" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="59" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="60" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="61" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="62" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="63" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="64" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="65" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="66" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="67" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="68" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="69" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="70" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="71" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="72" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="73" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="74" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="75" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="76" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="77" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="78" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="79" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="80" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="81" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="82" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="83" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="84" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="85" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="86" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="87" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="88" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="89" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="90" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="91" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="92" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="93" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="94" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="95" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="96" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="97" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="98" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="99" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="100" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="101" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="102" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="103" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="104" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="105" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="106" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="107" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="108" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="109" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="110" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="111" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="112" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="113" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="114" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="115" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="116" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="117" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="118" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="119" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="120" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="121" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="122" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="123" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="124" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="125" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="126" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="127" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="128" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="129" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="130" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="131" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="132" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="133" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="134" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="135" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="136" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="137" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="138" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="139" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="140" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="141" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="142" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="143" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="144" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="145" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="146" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="147" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="148" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="149" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="150" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="151" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="152" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="153" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="154" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="155" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="156" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="157" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="158" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="159" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="160" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="161" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="162" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="163" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="164" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="165" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="166" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="167" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="168" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="169" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="170" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="171" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="172" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="173" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="174" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="175" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="176" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="177" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="178" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="179" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="180" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="181" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="182" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="183" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="184" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="185" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="186" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="187" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="188" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="189" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="190" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="191" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="192" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="193" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="194" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="195" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="196" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="197" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="198" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="199" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="200" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="201" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="202" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="203" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="204" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="205" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="206" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="207" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="208" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="209" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="210" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="211" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="212" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="213" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="214" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="215" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="216" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="217" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="218" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="219" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="220" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="221" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="222" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="223" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="224" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="225" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="226" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="227" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="228" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="229" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="230" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="231" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="232" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="233" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="234" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="235" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="236" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="237" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="238" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="239" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="240" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="241" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="242" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="243" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="244" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="245" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="246" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="247" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="248" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="249" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="250" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="251" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="252" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="253" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="254" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="255" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="256" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="257" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="258" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="259" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="260" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="261" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="262" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="263" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="264" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="265" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="266" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="267" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="268" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="269" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="270" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="271" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="272" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="273" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="274" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="275" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="276" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="277" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="278" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="279" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="280" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="281" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="282" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="283" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="284" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="285" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="286" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="287" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="288" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="289" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="290" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="291" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="292" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="293" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="294" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="295" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="296" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="297" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="298" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="299" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="300" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="301" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="302" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="303" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="304" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="305" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="306" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="307" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="308" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="309" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="310" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="311" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="312" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="313" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="314" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="315" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="316" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="317" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="318" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="319" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="320" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="321" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="322" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="323" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="324" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="325" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="326" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="327" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="328" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="329" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="330" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="331" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="332" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="333" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="334" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="335" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="336" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="337" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="338" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="339" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="340" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="341" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="342" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="343" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="344" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="345" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="346" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="347" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="348" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="349" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="350" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="351" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="352" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="353" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="354" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="355" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="356" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="357" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="358" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="359" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="360" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="361" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="362" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="363" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="364" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="365" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="366" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="367" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="368" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="369" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="370" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="371" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="372" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="373" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="374" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="375" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="376" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="377" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="378" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="379" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="380" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="381" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="382" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="383" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="384" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="385" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="386" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="387" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="388" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="389" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="390" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="391" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="392" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="393" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="394" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="395" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="396" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="397" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="398" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="399" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="400" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="401" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="402" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="403" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="404" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="405" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="406" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="407" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="408" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="409" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="410" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="411" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="412" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="413" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="414" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="415" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="416" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="417" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="418" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="419" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="420" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="421" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="422" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="423" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="424" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="425" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="426" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="427" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="428" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="429" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="430" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="431" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="432" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="433" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="434" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="435" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="436" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="437" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="438" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="439" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="440" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="441" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="442" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="443" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="444" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="445" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="446" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="447" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="448" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="449" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="450" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="451" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="452" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="453" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="454" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="455" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="456" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="457" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="458" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="459" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="460" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="461" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="462" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="463" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="464" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="465" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="466" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="467" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="468" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="469" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="470" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="471" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="472" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="473" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="474" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="475" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="476" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="477" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="478" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="479" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="480" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="481" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="482" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="483" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="484" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="485" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="486" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="487" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="488" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="489" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="490" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="491" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="492" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="493" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="494" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="495" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="496" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="497" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="498" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="499" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="500" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="501" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="502" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="503" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="504" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="505" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="506" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="507" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="508" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="509" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="510" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="511" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="512" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="513" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="514" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="515" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="516" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="517" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="518" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="519" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="520" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="521" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="522" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="523" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="524" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="525" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="526" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="527" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="528" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="529" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="530" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="531" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="532" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="533" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="534" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="535" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="536" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="537" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="538" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="539" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="540" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="541" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="542" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="543" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="544" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="545" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="546" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="547" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="548" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="549" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="550" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="551" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="552" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="553" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="554" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="555" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="556" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="557" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="558" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="559" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="560" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="561" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="562" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="563" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="564" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="565" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="566" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="567" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="568" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="569" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="570" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="571" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="572" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="573" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="574" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="575" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="576" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="577" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="578" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="579" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="580" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="581" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="582" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="583" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="584" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="585" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="586" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="587" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="588" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="589" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="590" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="591" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="592" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="593" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="594" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="595" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="596" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="597" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="598" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="599" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="600" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="601" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="602" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="603" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="604" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="605" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="606" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="607" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="608" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="609" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="610" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="611" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="612" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="613" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="614" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="615" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="616" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="617" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="618" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="619" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="620" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="621" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="622" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="623" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="624" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="625" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="626" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="627" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="628" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="629" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="630" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="631" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="632" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="633" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="634" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="635" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="636" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="637" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="638" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="639" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="640" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="641" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="642" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="643" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="644" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="645" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="646" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="647" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="648" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="649" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="650" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="651" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="652" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="653" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="654" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="655" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="656" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="657" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="658" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="659" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="660" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="661" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="662" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="663" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="664" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="665" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="666" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="667" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="668" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="669" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="670" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="671" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="672" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="673" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="674" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="675" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="676" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="677" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="678" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="679" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="680" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="681" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="682" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="683" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="684" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="685" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="686" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="687" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="688" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="689" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="690" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="691" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="692" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="693" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="694" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="695" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="696" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="697" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="698" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="699" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="700" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="701" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="702" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="703" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="704" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="705" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="706" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="707" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="708" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="709" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="710" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="711" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="712" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="713" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="714" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="715" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="716" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="717" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="718" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="719" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="720" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="721" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="722" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="723" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="724" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="725" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="726" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="727" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="728" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="729" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="730" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="731" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="732" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="733" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="734" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="735" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="736" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="737" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="738" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="739" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="740" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="741" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="742" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="743" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="744" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="745" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="746" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="747" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="748" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="749" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="750" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="751" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="752" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="753" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="754" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="755" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="756" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="757" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="758" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="759" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="760" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="761" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="762" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="763" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="764" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="765" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="766" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="767" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="768" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="769" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="770" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="771" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="772" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="773" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="774" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="775" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="776" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="777" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="778" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="779" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="780" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="781" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="782" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="783" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="784" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="785" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="786" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="787" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="788" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="789" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="790" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="791" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="792" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="793" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="794" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="795" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="796" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="797" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="798" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="799" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="800" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="801" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="802" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="803" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="804" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="805" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="806" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="807" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="808" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="809" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="810" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="811" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="812" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="813" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="814" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="815" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="816" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="817" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="818" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="819" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="820" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="821" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="822" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="823" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="824" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="825" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="826" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="827" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="828" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="829" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="830" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="831" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="832" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="833" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="834" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="835" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="836" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="837" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="838" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="839" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="840" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="841" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="842" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="843" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="844" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="845" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="846" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="847" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="848" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="849" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="850" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="851" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="852" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="853" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="854" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="855" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="856" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="857" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="858" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="859" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="860" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="861" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="862" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="863" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="864" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="865" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="866" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="867" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="868" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="869" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="870" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="871" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="872" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="873" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="874" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="875" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="876" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="877" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="878" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="879" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="880" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="881" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="882" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="883" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="884" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="885" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="886" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="887" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="888" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="889" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="890" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="891" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="892" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="893" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="894" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="895" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="896" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="897" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="898" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="899" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="900" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="901" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="902" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="903" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="904" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="905" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="906" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="907" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="908" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="909" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="910" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="911" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="912" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="913" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="914" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="915" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="916" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="917" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="918" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="919" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="920" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="921" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="922" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="923" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="924" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="925" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="926" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="927" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="928" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="929" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="930" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="931" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="932" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="933" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="934" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="935" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="936" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="937" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="938" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="939" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="940" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="941" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="942" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="943" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="944" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="945" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="946" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="947" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="948" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="949" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="950" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="951" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="952" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="953" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="954" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="955" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="956" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="957" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="958" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="959" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="960" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="961" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="962" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="963" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="964" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="965" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="966" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="967" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="968" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="969" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="970" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="971" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="972" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="973" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="974" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="975" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="976" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="977" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="978" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="979" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="980" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="981" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="982" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="983" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="984" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="985" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="986" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="987" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="988" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="989" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="990" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="991" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="992" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="993" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="994" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="995" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="996" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="997" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="998" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="999" ht="12.75" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
@@ -2517,322 +2057,322 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:I500"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5546875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="29.6640625" style="10" customWidth="1"/>
-    <col min="2" max="2" width="13.88671875" style="10" customWidth="1"/>
-    <col min="3" max="3" width="9.33203125" style="10" customWidth="1"/>
-    <col min="4" max="4" width="61.77734375" style="10" customWidth="1"/>
-    <col min="5" max="5" width="9.88671875" style="10" customWidth="1"/>
-    <col min="6" max="6" width="9.5546875" style="10" customWidth="1"/>
-    <col min="7" max="7" width="36.21875" style="10" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" style="10" customWidth="1"/>
-    <col min="9" max="9" width="7.44140625" style="10" customWidth="1"/>
+    <col min="1" max="1" width="29.7109375" style="6" customWidth="1"/>
+    <col min="2" max="2" width="13.85546875" style="6" customWidth="1"/>
+    <col min="3" max="3" width="9.28515625" style="6" customWidth="1"/>
+    <col min="4" max="4" width="61.7109375" style="6" customWidth="1"/>
+    <col min="5" max="5" width="9.85546875" style="6" customWidth="1"/>
+    <col min="6" max="6" width="9.5703125" style="6" customWidth="1"/>
+    <col min="7" max="7" width="36.28515625" style="6" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" style="6" customWidth="1"/>
+    <col min="9" max="9" width="7.42578125" style="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+    </row>
+    <row r="2" spans="1:9" ht="51" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-    </row>
-    <row r="2" spans="1:9" ht="52.8" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="G2" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G2" s="20" t="s">
-        <v>110</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="57" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
+    </row>
+    <row r="3" spans="1:9" ht="60" x14ac:dyDescent="0.2">
+      <c r="A3" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="G3"/>
+      <c r="H3" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="I3" s="11"/>
+    </row>
+    <row r="4" spans="1:9" ht="24" x14ac:dyDescent="0.2">
+      <c r="A4" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="B4" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="C4" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="D4" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4"/>
+      <c r="H4" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="I4" s="11"/>
+    </row>
+    <row r="5" spans="1:9" ht="36" x14ac:dyDescent="0.2">
+      <c r="A5" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15" t="s">
+      <c r="B5" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="G3"/>
-      <c r="H3" s="15" t="s">
+      <c r="C5" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="D5" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="I3" s="15"/>
-    </row>
-    <row r="4" spans="1:9" ht="22.8" x14ac:dyDescent="0.25">
-      <c r="A4" s="14" t="s">
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5"/>
+      <c r="H5" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="I5" s="11"/>
+    </row>
+    <row r="6" spans="1:9" ht="48" x14ac:dyDescent="0.2">
+      <c r="A6" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B6" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="C4" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="D4" s="15" t="s">
+      <c r="C6" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="D6" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="E4" s="15"/>
-      <c r="F4" s="15"/>
-      <c r="G4"/>
-      <c r="H4" s="15" t="s">
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="I6" s="11"/>
+    </row>
+    <row r="7" spans="1:9" ht="24" x14ac:dyDescent="0.2">
+      <c r="A7" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="I4" s="15"/>
-    </row>
-    <row r="5" spans="1:9" ht="34.200000000000003" x14ac:dyDescent="0.25">
-      <c r="A5" s="14" t="s">
+      <c r="B7" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="C7" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="D7" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="C5" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="D5" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="E5" s="15"/>
-      <c r="F5" s="15"/>
-      <c r="G5"/>
-      <c r="H5" s="15" t="s">
-        <v>74</v>
-      </c>
-      <c r="I5" s="15"/>
-    </row>
-    <row r="6" spans="1:9" ht="45.6" x14ac:dyDescent="0.25">
-      <c r="A6" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="B6" s="15" t="s">
-        <v>79</v>
-      </c>
-      <c r="C6" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="D6" s="15" t="s">
-        <v>80</v>
-      </c>
-      <c r="E6" s="15"/>
-      <c r="F6" s="15"/>
-      <c r="G6" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="H6" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="I6" s="15"/>
-    </row>
-    <row r="7" spans="1:9" ht="22.8" x14ac:dyDescent="0.25">
-      <c r="A7" s="14" t="s">
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+      <c r="G7"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="11"/>
+    </row>
+    <row r="8" spans="1:9" ht="24" x14ac:dyDescent="0.2">
+      <c r="A8" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="B8" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="D8" s="11" t="s">
         <v>82</v>
-      </c>
-      <c r="C7" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="D7" s="15" t="s">
-        <v>83</v>
-      </c>
-      <c r="E7" s="15"/>
-      <c r="F7" s="15"/>
-      <c r="G7"/>
-      <c r="H7" s="15"/>
-      <c r="I7" s="15"/>
-    </row>
-    <row r="8" spans="1:9" ht="22.8" x14ac:dyDescent="0.25">
-      <c r="A8" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="B8" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="C8" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="D8" s="15" t="s">
-        <v>89</v>
       </c>
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
-      <c r="G8" s="14" t="s">
-        <v>65</v>
+      <c r="G8" s="10" t="s">
+        <v>58</v>
       </c>
       <c r="H8" s="4"/>
       <c r="I8" s="4"/>
     </row>
-    <row r="9" spans="1:9" ht="34.200000000000003" x14ac:dyDescent="0.25">
-      <c r="A9" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="B9" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="C9" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="D9" s="15" t="s">
-        <v>93</v>
+    <row r="9" spans="1:9" ht="36" x14ac:dyDescent="0.2">
+      <c r="A9" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>86</v>
       </c>
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
-      <c r="G9" s="14" t="s">
-        <v>65</v>
+      <c r="G9" s="10" t="s">
+        <v>58</v>
       </c>
       <c r="H9" s="4"/>
       <c r="I9" s="4"/>
     </row>
-    <row r="10" spans="1:9" ht="45.6" x14ac:dyDescent="0.25">
-      <c r="A10" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="B10" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="C10" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="D10" s="15" t="s">
-        <v>96</v>
+    <row r="10" spans="1:9" ht="48" x14ac:dyDescent="0.2">
+      <c r="A10" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>89</v>
       </c>
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
-      <c r="G10" s="14" t="s">
-        <v>65</v>
+      <c r="G10" s="10" t="s">
+        <v>58</v>
       </c>
       <c r="H10" s="4"/>
       <c r="I10" s="4"/>
     </row>
-    <row r="11" spans="1:9" ht="22.8" x14ac:dyDescent="0.25">
-      <c r="A11" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="B11" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="C11" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="D11" s="15" t="s">
-        <v>98</v>
+    <row r="11" spans="1:9" ht="24" x14ac:dyDescent="0.2">
+      <c r="A11" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>91</v>
       </c>
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
-      <c r="G11" s="14" t="s">
-        <v>81</v>
+      <c r="G11" s="10" t="s">
+        <v>74</v>
       </c>
       <c r="H11" s="4"/>
       <c r="I11" s="4"/>
     </row>
-    <row r="12" spans="1:9" ht="22.8" x14ac:dyDescent="0.25">
-      <c r="A12" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="B12" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="C12" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="D12" s="15" t="s">
-        <v>105</v>
+    <row r="12" spans="1:9" ht="24" x14ac:dyDescent="0.2">
+      <c r="A12" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>98</v>
       </c>
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
-      <c r="G12" s="14" t="s">
-        <v>75</v>
+      <c r="G12" s="10" t="s">
+        <v>68</v>
       </c>
       <c r="H12" s="4"/>
       <c r="I12" s="4"/>
     </row>
-    <row r="13" spans="1:9" ht="34.200000000000003" x14ac:dyDescent="0.25">
-      <c r="A13" s="14" t="s">
-        <v>100</v>
-      </c>
-      <c r="B13" s="15" t="s">
-        <v>101</v>
-      </c>
-      <c r="C13" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="D13" s="15" t="s">
-        <v>106</v>
+    <row r="13" spans="1:9" ht="48" x14ac:dyDescent="0.2">
+      <c r="A13" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>99</v>
       </c>
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
-      <c r="G13" s="14" t="s">
-        <v>75</v>
+      <c r="G13" s="10" t="s">
+        <v>68</v>
       </c>
       <c r="H13" s="4"/>
       <c r="I13" s="4"/>
     </row>
-    <row r="14" spans="1:9" ht="22.8" x14ac:dyDescent="0.25">
-      <c r="A14" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="B14" s="15" t="s">
-        <v>104</v>
-      </c>
-      <c r="C14" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="D14" s="15" t="s">
-        <v>107</v>
+    <row r="14" spans="1:9" ht="36" x14ac:dyDescent="0.2">
+      <c r="A14" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>100</v>
       </c>
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
-      <c r="G14" s="14" t="s">
-        <v>75</v>
+      <c r="G14" s="10" t="s">
+        <v>68</v>
       </c>
       <c r="H14" s="4"/>
       <c r="I14" s="4"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="4"/>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
@@ -2843,7 +2383,7 @@
       <c r="H15" s="4"/>
       <c r="I15" s="4"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" s="4"/>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
@@ -2854,7 +2394,7 @@
       <c r="H16" s="4"/>
       <c r="I16" s="4"/>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="4"/>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
@@ -2865,7 +2405,7 @@
       <c r="H17" s="4"/>
       <c r="I17" s="4"/>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" s="4"/>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
@@ -2876,7 +2416,7 @@
       <c r="H18" s="4"/>
       <c r="I18" s="4"/>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="4"/>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
@@ -2887,7 +2427,7 @@
       <c r="H19" s="4"/>
       <c r="I19" s="4"/>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" s="4"/>
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
@@ -2898,7 +2438,7 @@
       <c r="H20" s="4"/>
       <c r="I20" s="4"/>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" s="4"/>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
@@ -2909,7 +2449,7 @@
       <c r="H21" s="4"/>
       <c r="I21" s="4"/>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" s="4"/>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
@@ -2920,7 +2460,7 @@
       <c r="H22" s="4"/>
       <c r="I22" s="4"/>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" s="4"/>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
@@ -2931,7 +2471,7 @@
       <c r="H23" s="4"/>
       <c r="I23" s="4"/>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" s="4"/>
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
@@ -2942,7 +2482,7 @@
       <c r="H24" s="4"/>
       <c r="I24" s="4"/>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" s="4"/>
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
@@ -2953,7 +2493,7 @@
       <c r="H25" s="4"/>
       <c r="I25" s="4"/>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" s="4"/>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
@@ -2964,7 +2504,7 @@
       <c r="H26" s="4"/>
       <c r="I26" s="4"/>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" s="4"/>
       <c r="B27" s="4"/>
       <c r="C27" s="4"/>
@@ -2975,7 +2515,7 @@
       <c r="H27" s="4"/>
       <c r="I27" s="4"/>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" s="4"/>
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
@@ -2986,7 +2526,7 @@
       <c r="H28" s="4"/>
       <c r="I28" s="4"/>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" s="4"/>
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
@@ -2997,7 +2537,7 @@
       <c r="H29" s="4"/>
       <c r="I29" s="4"/>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" s="4"/>
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
@@ -3008,7 +2548,7 @@
       <c r="H30" s="4"/>
       <c r="I30" s="4"/>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" s="4"/>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
@@ -3019,7 +2559,7 @@
       <c r="H31" s="4"/>
       <c r="I31" s="4"/>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" s="4"/>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
@@ -3030,7 +2570,7 @@
       <c r="H32" s="4"/>
       <c r="I32" s="4"/>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33" s="4"/>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
@@ -3041,7 +2581,7 @@
       <c r="H33" s="4"/>
       <c r="I33" s="4"/>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" s="4"/>
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
@@ -3052,7 +2592,7 @@
       <c r="H34" s="4"/>
       <c r="I34" s="4"/>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35" s="4"/>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
@@ -3063,7 +2603,7 @@
       <c r="H35" s="4"/>
       <c r="I35" s="4"/>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A36" s="4"/>
       <c r="B36" s="4"/>
       <c r="C36" s="4"/>
@@ -3074,7 +2614,7 @@
       <c r="H36" s="4"/>
       <c r="I36" s="4"/>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A37" s="4"/>
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
@@ -3085,7 +2625,7 @@
       <c r="H37" s="4"/>
       <c r="I37" s="4"/>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38" s="4"/>
       <c r="B38" s="4"/>
       <c r="C38" s="4"/>
@@ -3096,7 +2636,7 @@
       <c r="H38" s="4"/>
       <c r="I38" s="4"/>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A39" s="4"/>
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
@@ -3107,7 +2647,7 @@
       <c r="H39" s="4"/>
       <c r="I39" s="4"/>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A40" s="4"/>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
@@ -3118,7 +2658,7 @@
       <c r="H40" s="4"/>
       <c r="I40" s="4"/>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
@@ -3129,7 +2669,7 @@
       <c r="H41" s="4"/>
       <c r="I41" s="4"/>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A42" s="4"/>
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
@@ -3140,7 +2680,7 @@
       <c r="H42" s="4"/>
       <c r="I42" s="4"/>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A43" s="4"/>
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
@@ -3151,7 +2691,7 @@
       <c r="H43" s="4"/>
       <c r="I43" s="4"/>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A44" s="4"/>
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
@@ -3162,7 +2702,7 @@
       <c r="H44" s="4"/>
       <c r="I44" s="4"/>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A45" s="4"/>
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
@@ -3173,7 +2713,7 @@
       <c r="H45" s="4"/>
       <c r="I45" s="4"/>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A46" s="4"/>
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
@@ -3184,7 +2724,7 @@
       <c r="H46" s="4"/>
       <c r="I46" s="4"/>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A47" s="4"/>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
@@ -3195,7 +2735,7 @@
       <c r="H47" s="4"/>
       <c r="I47" s="4"/>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A48" s="4"/>
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
@@ -3206,7 +2746,7 @@
       <c r="H48" s="4"/>
       <c r="I48" s="4"/>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A49" s="4"/>
       <c r="B49" s="4"/>
       <c r="C49" s="4"/>
@@ -3217,7 +2757,7 @@
       <c r="H49" s="4"/>
       <c r="I49" s="4"/>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A50" s="4"/>
       <c r="B50" s="4"/>
       <c r="C50" s="4"/>
@@ -3228,7 +2768,7 @@
       <c r="H50" s="4"/>
       <c r="I50" s="4"/>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A51" s="4"/>
       <c r="B51" s="4"/>
       <c r="C51" s="4"/>
@@ -3239,7 +2779,7 @@
       <c r="H51" s="4"/>
       <c r="I51" s="4"/>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A52" s="4"/>
       <c r="B52" s="4"/>
       <c r="C52" s="4"/>
@@ -3250,7 +2790,7 @@
       <c r="H52" s="4"/>
       <c r="I52" s="4"/>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A53" s="4"/>
       <c r="B53" s="4"/>
       <c r="C53" s="4"/>
@@ -3261,7 +2801,7 @@
       <c r="H53" s="4"/>
       <c r="I53" s="4"/>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A54" s="4"/>
       <c r="B54" s="4"/>
       <c r="C54" s="4"/>
@@ -3272,7 +2812,7 @@
       <c r="H54" s="4"/>
       <c r="I54" s="4"/>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A55" s="4"/>
       <c r="B55" s="4"/>
       <c r="C55" s="4"/>
@@ -3283,7 +2823,7 @@
       <c r="H55" s="4"/>
       <c r="I55" s="4"/>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A56" s="4"/>
       <c r="B56" s="4"/>
       <c r="C56" s="4"/>
@@ -3294,7 +2834,7 @@
       <c r="H56" s="4"/>
       <c r="I56" s="4"/>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A57" s="4"/>
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
@@ -3305,7 +2845,7 @@
       <c r="H57" s="4"/>
       <c r="I57" s="4"/>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A58" s="4"/>
       <c r="B58" s="4"/>
       <c r="C58" s="4"/>
@@ -3316,7 +2856,7 @@
       <c r="H58" s="4"/>
       <c r="I58" s="4"/>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A59" s="4"/>
       <c r="B59" s="4"/>
       <c r="C59" s="4"/>
@@ -3327,7 +2867,7 @@
       <c r="H59" s="4"/>
       <c r="I59" s="4"/>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A60" s="4"/>
       <c r="B60" s="4"/>
       <c r="C60" s="4"/>
@@ -3338,7 +2878,7 @@
       <c r="H60" s="4"/>
       <c r="I60" s="4"/>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A61" s="4"/>
       <c r="B61" s="4"/>
       <c r="C61" s="4"/>
@@ -3349,7 +2889,7 @@
       <c r="H61" s="4"/>
       <c r="I61" s="4"/>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A62" s="4"/>
       <c r="B62" s="4"/>
       <c r="C62" s="4"/>
@@ -3360,7 +2900,7 @@
       <c r="H62" s="4"/>
       <c r="I62" s="4"/>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A63" s="4"/>
       <c r="B63" s="4"/>
       <c r="C63" s="4"/>
@@ -3371,7 +2911,7 @@
       <c r="H63" s="4"/>
       <c r="I63" s="4"/>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A64" s="4"/>
       <c r="B64" s="4"/>
       <c r="C64" s="4"/>
@@ -3382,7 +2922,7 @@
       <c r="H64" s="4"/>
       <c r="I64" s="4"/>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A65" s="4"/>
       <c r="B65" s="4"/>
       <c r="C65" s="4"/>
@@ -3393,7 +2933,7 @@
       <c r="H65" s="4"/>
       <c r="I65" s="4"/>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A66" s="4"/>
       <c r="B66" s="4"/>
       <c r="C66" s="4"/>
@@ -3404,7 +2944,7 @@
       <c r="H66" s="4"/>
       <c r="I66" s="4"/>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A67" s="4"/>
       <c r="B67" s="4"/>
       <c r="C67" s="4"/>
@@ -3415,7 +2955,7 @@
       <c r="H67" s="4"/>
       <c r="I67" s="4"/>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A68" s="4"/>
       <c r="B68" s="4"/>
       <c r="C68" s="4"/>
@@ -3426,7 +2966,7 @@
       <c r="H68" s="4"/>
       <c r="I68" s="4"/>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A69" s="4"/>
       <c r="B69" s="4"/>
       <c r="C69" s="4"/>
@@ -3437,7 +2977,7 @@
       <c r="H69" s="4"/>
       <c r="I69" s="4"/>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A70" s="4"/>
       <c r="B70" s="4"/>
       <c r="C70" s="4"/>
@@ -3448,7 +2988,7 @@
       <c r="H70" s="4"/>
       <c r="I70" s="4"/>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A71" s="4"/>
       <c r="B71" s="4"/>
       <c r="C71" s="4"/>
@@ -3459,7 +2999,7 @@
       <c r="H71" s="4"/>
       <c r="I71" s="4"/>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A72" s="4"/>
       <c r="B72" s="4"/>
       <c r="C72" s="4"/>
@@ -3470,7 +3010,7 @@
       <c r="H72" s="4"/>
       <c r="I72" s="4"/>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A73" s="4"/>
       <c r="B73" s="4"/>
       <c r="C73" s="4"/>
@@ -3481,7 +3021,7 @@
       <c r="H73" s="4"/>
       <c r="I73" s="4"/>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A74" s="4"/>
       <c r="B74" s="4"/>
       <c r="C74" s="4"/>
@@ -3492,7 +3032,7 @@
       <c r="H74" s="4"/>
       <c r="I74" s="4"/>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A75" s="4"/>
       <c r="B75" s="4"/>
       <c r="C75" s="4"/>
@@ -3503,7 +3043,7 @@
       <c r="H75" s="4"/>
       <c r="I75" s="4"/>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A76" s="4"/>
       <c r="B76" s="4"/>
       <c r="C76" s="4"/>
@@ -3514,7 +3054,7 @@
       <c r="H76" s="4"/>
       <c r="I76" s="4"/>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A77" s="4"/>
       <c r="B77" s="4"/>
       <c r="C77" s="4"/>
@@ -3525,7 +3065,7 @@
       <c r="H77" s="4"/>
       <c r="I77" s="4"/>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A78" s="4"/>
       <c r="B78" s="4"/>
       <c r="C78" s="4"/>
@@ -3536,7 +3076,7 @@
       <c r="H78" s="4"/>
       <c r="I78" s="4"/>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A79" s="4"/>
       <c r="B79" s="4"/>
       <c r="C79" s="4"/>
@@ -3547,7 +3087,7 @@
       <c r="H79" s="4"/>
       <c r="I79" s="4"/>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A80" s="4"/>
       <c r="B80" s="4"/>
       <c r="C80" s="4"/>
@@ -3558,7 +3098,7 @@
       <c r="H80" s="4"/>
       <c r="I80" s="4"/>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A81" s="4"/>
       <c r="B81" s="4"/>
       <c r="C81" s="4"/>
@@ -3569,7 +3109,7 @@
       <c r="H81" s="4"/>
       <c r="I81" s="4"/>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A82" s="4"/>
       <c r="B82" s="4"/>
       <c r="C82" s="4"/>
@@ -3580,7 +3120,7 @@
       <c r="H82" s="4"/>
       <c r="I82" s="4"/>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A83" s="4"/>
       <c r="B83" s="4"/>
       <c r="C83" s="4"/>
@@ -3591,7 +3131,7 @@
       <c r="H83" s="4"/>
       <c r="I83" s="4"/>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A84" s="4"/>
       <c r="B84" s="4"/>
       <c r="C84" s="4"/>
@@ -3602,7 +3142,7 @@
       <c r="H84" s="4"/>
       <c r="I84" s="4"/>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A85" s="4"/>
       <c r="B85" s="4"/>
       <c r="C85" s="4"/>
@@ -3613,7 +3153,7 @@
       <c r="H85" s="4"/>
       <c r="I85" s="4"/>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A86" s="4"/>
       <c r="B86" s="4"/>
       <c r="C86" s="4"/>
@@ -3624,7 +3164,7 @@
       <c r="H86" s="4"/>
       <c r="I86" s="4"/>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A87" s="4"/>
       <c r="B87" s="4"/>
       <c r="C87" s="4"/>
@@ -3635,7 +3175,7 @@
       <c r="H87" s="4"/>
       <c r="I87" s="4"/>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A88" s="4"/>
       <c r="B88" s="4"/>
       <c r="C88" s="4"/>
@@ -3646,7 +3186,7 @@
       <c r="H88" s="4"/>
       <c r="I88" s="4"/>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A89" s="4"/>
       <c r="B89" s="4"/>
       <c r="C89" s="4"/>
@@ -3657,7 +3197,7 @@
       <c r="H89" s="4"/>
       <c r="I89" s="4"/>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A90" s="4"/>
       <c r="B90" s="4"/>
       <c r="C90" s="4"/>
@@ -3668,7 +3208,7 @@
       <c r="H90" s="4"/>
       <c r="I90" s="4"/>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A91" s="4"/>
       <c r="B91" s="4"/>
       <c r="C91" s="4"/>
@@ -3679,7 +3219,7 @@
       <c r="H91" s="4"/>
       <c r="I91" s="4"/>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A92" s="4"/>
       <c r="B92" s="4"/>
       <c r="C92" s="4"/>
@@ -3690,7 +3230,7 @@
       <c r="H92" s="4"/>
       <c r="I92" s="4"/>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A93" s="4"/>
       <c r="B93" s="4"/>
       <c r="C93" s="4"/>
@@ -3701,7 +3241,7 @@
       <c r="H93" s="4"/>
       <c r="I93" s="4"/>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A94" s="4"/>
       <c r="B94" s="4"/>
       <c r="C94" s="4"/>
@@ -3712,7 +3252,7 @@
       <c r="H94" s="4"/>
       <c r="I94" s="4"/>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A95" s="4"/>
       <c r="B95" s="4"/>
       <c r="C95" s="4"/>
@@ -3723,7 +3263,7 @@
       <c r="H95" s="4"/>
       <c r="I95" s="4"/>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A96" s="4"/>
       <c r="B96" s="4"/>
       <c r="C96" s="4"/>
@@ -3734,7 +3274,7 @@
       <c r="H96" s="4"/>
       <c r="I96" s="4"/>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A97" s="4"/>
       <c r="B97" s="4"/>
       <c r="C97" s="4"/>
@@ -3745,7 +3285,7 @@
       <c r="H97" s="4"/>
       <c r="I97" s="4"/>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A98" s="4"/>
       <c r="B98" s="4"/>
       <c r="C98" s="4"/>
@@ -3756,7 +3296,7 @@
       <c r="H98" s="4"/>
       <c r="I98" s="4"/>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A99" s="4"/>
       <c r="B99" s="4"/>
       <c r="C99" s="4"/>
@@ -3767,7 +3307,7 @@
       <c r="H99" s="4"/>
       <c r="I99" s="4"/>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A100" s="4"/>
       <c r="B100" s="4"/>
       <c r="C100" s="4"/>
@@ -3778,7 +3318,7 @@
       <c r="H100" s="4"/>
       <c r="I100" s="4"/>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A101" s="4"/>
       <c r="B101" s="4"/>
       <c r="C101" s="4"/>
@@ -3789,7 +3329,7 @@
       <c r="H101" s="4"/>
       <c r="I101" s="4"/>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A102" s="4"/>
       <c r="B102" s="4"/>
       <c r="C102" s="4"/>
@@ -3800,7 +3340,7 @@
       <c r="H102" s="4"/>
       <c r="I102" s="4"/>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A103" s="4"/>
       <c r="B103" s="4"/>
       <c r="C103" s="4"/>
@@ -3811,7 +3351,7 @@
       <c r="H103" s="4"/>
       <c r="I103" s="4"/>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A104" s="4"/>
       <c r="B104" s="4"/>
       <c r="C104" s="4"/>
@@ -3822,7 +3362,7 @@
       <c r="H104" s="4"/>
       <c r="I104" s="4"/>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A105" s="4"/>
       <c r="B105" s="4"/>
       <c r="C105" s="4"/>
@@ -3833,7 +3373,7 @@
       <c r="H105" s="4"/>
       <c r="I105" s="4"/>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A106" s="4"/>
       <c r="B106" s="4"/>
       <c r="C106" s="4"/>
@@ -3844,7 +3384,7 @@
       <c r="H106" s="4"/>
       <c r="I106" s="4"/>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A107" s="4"/>
       <c r="B107" s="4"/>
       <c r="C107" s="4"/>
@@ -3855,7 +3395,7 @@
       <c r="H107" s="4"/>
       <c r="I107" s="4"/>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A108" s="4"/>
       <c r="B108" s="4"/>
       <c r="C108" s="4"/>
@@ -3866,7 +3406,7 @@
       <c r="H108" s="4"/>
       <c r="I108" s="4"/>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A109" s="4"/>
       <c r="B109" s="4"/>
       <c r="C109" s="4"/>
@@ -3877,7 +3417,7 @@
       <c r="H109" s="4"/>
       <c r="I109" s="4"/>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A110" s="4"/>
       <c r="B110" s="4"/>
       <c r="C110" s="4"/>
@@ -3888,7 +3428,7 @@
       <c r="H110" s="4"/>
       <c r="I110" s="4"/>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A111" s="4"/>
       <c r="B111" s="4"/>
       <c r="C111" s="4"/>
@@ -3899,7 +3439,7 @@
       <c r="H111" s="4"/>
       <c r="I111" s="4"/>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A112" s="4"/>
       <c r="B112" s="4"/>
       <c r="C112" s="4"/>
@@ -3910,7 +3450,7 @@
       <c r="H112" s="4"/>
       <c r="I112" s="4"/>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A113" s="4"/>
       <c r="B113" s="4"/>
       <c r="C113" s="4"/>
@@ -3921,7 +3461,7 @@
       <c r="H113" s="4"/>
       <c r="I113" s="4"/>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A114" s="4"/>
       <c r="B114" s="4"/>
       <c r="C114" s="4"/>
@@ -3932,7 +3472,7 @@
       <c r="H114" s="4"/>
       <c r="I114" s="4"/>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A115" s="4"/>
       <c r="B115" s="4"/>
       <c r="C115" s="4"/>
@@ -3943,7 +3483,7 @@
       <c r="H115" s="4"/>
       <c r="I115" s="4"/>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A116" s="4"/>
       <c r="B116" s="4"/>
       <c r="C116" s="4"/>
@@ -3954,7 +3494,7 @@
       <c r="H116" s="4"/>
       <c r="I116" s="4"/>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A117" s="4"/>
       <c r="B117" s="4"/>
       <c r="C117" s="4"/>
@@ -3965,7 +3505,7 @@
       <c r="H117" s="4"/>
       <c r="I117" s="4"/>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A118" s="4"/>
       <c r="B118" s="4"/>
       <c r="C118" s="4"/>
@@ -3976,7 +3516,7 @@
       <c r="H118" s="4"/>
       <c r="I118" s="4"/>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A119" s="4"/>
       <c r="B119" s="4"/>
       <c r="C119" s="4"/>
@@ -3987,7 +3527,7 @@
       <c r="H119" s="4"/>
       <c r="I119" s="4"/>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A120" s="4"/>
       <c r="B120" s="4"/>
       <c r="C120" s="4"/>
@@ -3998,7 +3538,7 @@
       <c r="H120" s="4"/>
       <c r="I120" s="4"/>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A121" s="4"/>
       <c r="B121" s="4"/>
       <c r="C121" s="4"/>
@@ -4009,7 +3549,7 @@
       <c r="H121" s="4"/>
       <c r="I121" s="4"/>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A122" s="4"/>
       <c r="B122" s="4"/>
       <c r="C122" s="4"/>
@@ -4020,7 +3560,7 @@
       <c r="H122" s="4"/>
       <c r="I122" s="4"/>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A123" s="4"/>
       <c r="B123" s="4"/>
       <c r="C123" s="4"/>
@@ -4031,7 +3571,7 @@
       <c r="H123" s="4"/>
       <c r="I123" s="4"/>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A124" s="4"/>
       <c r="B124" s="4"/>
       <c r="C124" s="4"/>
@@ -4042,7 +3582,7 @@
       <c r="H124" s="4"/>
       <c r="I124" s="4"/>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A125" s="4"/>
       <c r="B125" s="4"/>
       <c r="C125" s="4"/>
@@ -4053,7 +3593,7 @@
       <c r="H125" s="4"/>
       <c r="I125" s="4"/>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A126" s="4"/>
       <c r="B126" s="4"/>
       <c r="C126" s="4"/>
@@ -4064,7 +3604,7 @@
       <c r="H126" s="4"/>
       <c r="I126" s="4"/>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A127" s="4"/>
       <c r="B127" s="4"/>
       <c r="C127" s="4"/>
@@ -4075,7 +3615,7 @@
       <c r="H127" s="4"/>
       <c r="I127" s="4"/>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A128" s="4"/>
       <c r="B128" s="4"/>
       <c r="C128" s="4"/>
@@ -4086,7 +3626,7 @@
       <c r="H128" s="4"/>
       <c r="I128" s="4"/>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A129" s="4"/>
       <c r="B129" s="4"/>
       <c r="C129" s="4"/>
@@ -4097,7 +3637,7 @@
       <c r="H129" s="4"/>
       <c r="I129" s="4"/>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A130" s="4"/>
       <c r="B130" s="4"/>
       <c r="C130" s="4"/>
@@ -4108,7 +3648,7 @@
       <c r="H130" s="4"/>
       <c r="I130" s="4"/>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A131" s="4"/>
       <c r="B131" s="4"/>
       <c r="C131" s="4"/>
@@ -4119,7 +3659,7 @@
       <c r="H131" s="4"/>
       <c r="I131" s="4"/>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A132" s="4"/>
       <c r="B132" s="4"/>
       <c r="C132" s="4"/>
@@ -4130,7 +3670,7 @@
       <c r="H132" s="4"/>
       <c r="I132" s="4"/>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A133" s="4"/>
       <c r="B133" s="4"/>
       <c r="C133" s="4"/>
@@ -4141,7 +3681,7 @@
       <c r="H133" s="4"/>
       <c r="I133" s="4"/>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A134" s="4"/>
       <c r="B134" s="4"/>
       <c r="C134" s="4"/>
@@ -4152,7 +3692,7 @@
       <c r="H134" s="4"/>
       <c r="I134" s="4"/>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A135" s="4"/>
       <c r="B135" s="4"/>
       <c r="C135" s="4"/>
@@ -4163,7 +3703,7 @@
       <c r="H135" s="4"/>
       <c r="I135" s="4"/>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A136" s="4"/>
       <c r="B136" s="4"/>
       <c r="C136" s="4"/>
@@ -4174,7 +3714,7 @@
       <c r="H136" s="4"/>
       <c r="I136" s="4"/>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A137" s="4"/>
       <c r="B137" s="4"/>
       <c r="C137" s="4"/>
@@ -4185,7 +3725,7 @@
       <c r="H137" s="4"/>
       <c r="I137" s="4"/>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A138" s="4"/>
       <c r="B138" s="4"/>
       <c r="C138" s="4"/>
@@ -4196,7 +3736,7 @@
       <c r="H138" s="4"/>
       <c r="I138" s="4"/>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A139" s="4"/>
       <c r="B139" s="4"/>
       <c r="C139" s="4"/>
@@ -4207,7 +3747,7 @@
       <c r="H139" s="4"/>
       <c r="I139" s="4"/>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A140" s="4"/>
       <c r="B140" s="4"/>
       <c r="C140" s="4"/>
@@ -4218,7 +3758,7 @@
       <c r="H140" s="4"/>
       <c r="I140" s="4"/>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A141" s="4"/>
       <c r="B141" s="4"/>
       <c r="C141" s="4"/>
@@ -4229,7 +3769,7 @@
       <c r="H141" s="4"/>
       <c r="I141" s="4"/>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A142" s="4"/>
       <c r="B142" s="4"/>
       <c r="C142" s="4"/>
@@ -4240,7 +3780,7 @@
       <c r="H142" s="4"/>
       <c r="I142" s="4"/>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A143" s="4"/>
       <c r="B143" s="4"/>
       <c r="C143" s="4"/>
@@ -4251,7 +3791,7 @@
       <c r="H143" s="4"/>
       <c r="I143" s="4"/>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A144" s="4"/>
       <c r="B144" s="4"/>
       <c r="C144" s="4"/>
@@ -4262,7 +3802,7 @@
       <c r="H144" s="4"/>
       <c r="I144" s="4"/>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A145" s="4"/>
       <c r="B145" s="4"/>
       <c r="C145" s="4"/>
@@ -4273,7 +3813,7 @@
       <c r="H145" s="4"/>
       <c r="I145" s="4"/>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A146" s="4"/>
       <c r="B146" s="4"/>
       <c r="C146" s="4"/>
@@ -4284,7 +3824,7 @@
       <c r="H146" s="4"/>
       <c r="I146" s="4"/>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A147" s="4"/>
       <c r="B147" s="4"/>
       <c r="C147" s="4"/>
@@ -4295,7 +3835,7 @@
       <c r="H147" s="4"/>
       <c r="I147" s="4"/>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A148" s="4"/>
       <c r="B148" s="4"/>
       <c r="C148" s="4"/>
@@ -4306,7 +3846,7 @@
       <c r="H148" s="4"/>
       <c r="I148" s="4"/>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A149" s="4"/>
       <c r="B149" s="4"/>
       <c r="C149" s="4"/>
@@ -4317,7 +3857,7 @@
       <c r="H149" s="4"/>
       <c r="I149" s="4"/>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A150" s="4"/>
       <c r="B150" s="4"/>
       <c r="C150" s="4"/>
@@ -4328,7 +3868,7 @@
       <c r="H150" s="4"/>
       <c r="I150" s="4"/>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A151" s="4"/>
       <c r="B151" s="4"/>
       <c r="C151" s="4"/>
@@ -4339,7 +3879,7 @@
       <c r="H151" s="4"/>
       <c r="I151" s="4"/>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A152" s="4"/>
       <c r="B152" s="4"/>
       <c r="C152" s="4"/>
@@ -4350,7 +3890,7 @@
       <c r="H152" s="4"/>
       <c r="I152" s="4"/>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A153" s="4"/>
       <c r="B153" s="4"/>
       <c r="C153" s="4"/>
@@ -4361,7 +3901,7 @@
       <c r="H153" s="4"/>
       <c r="I153" s="4"/>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A154" s="4"/>
       <c r="B154" s="4"/>
       <c r="C154" s="4"/>
@@ -4372,7 +3912,7 @@
       <c r="H154" s="4"/>
       <c r="I154" s="4"/>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A155" s="4"/>
       <c r="B155" s="4"/>
       <c r="C155" s="4"/>
@@ -4383,7 +3923,7 @@
       <c r="H155" s="4"/>
       <c r="I155" s="4"/>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A156" s="4"/>
       <c r="B156" s="4"/>
       <c r="C156" s="4"/>
@@ -4394,7 +3934,7 @@
       <c r="H156" s="4"/>
       <c r="I156" s="4"/>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A157" s="4"/>
       <c r="B157" s="4"/>
       <c r="C157" s="4"/>
@@ -4405,7 +3945,7 @@
       <c r="H157" s="4"/>
       <c r="I157" s="4"/>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A158" s="4"/>
       <c r="B158" s="4"/>
       <c r="C158" s="4"/>
@@ -4416,7 +3956,7 @@
       <c r="H158" s="4"/>
       <c r="I158" s="4"/>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A159" s="4"/>
       <c r="B159" s="4"/>
       <c r="C159" s="4"/>
@@ -4427,7 +3967,7 @@
       <c r="H159" s="4"/>
       <c r="I159" s="4"/>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A160" s="4"/>
       <c r="B160" s="4"/>
       <c r="C160" s="4"/>
@@ -4438,7 +3978,7 @@
       <c r="H160" s="4"/>
       <c r="I160" s="4"/>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A161" s="4"/>
       <c r="B161" s="4"/>
       <c r="C161" s="4"/>
@@ -4449,7 +3989,7 @@
       <c r="H161" s="4"/>
       <c r="I161" s="4"/>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A162" s="4"/>
       <c r="B162" s="4"/>
       <c r="C162" s="4"/>
@@ -4460,7 +4000,7 @@
       <c r="H162" s="4"/>
       <c r="I162" s="4"/>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A163" s="4"/>
       <c r="B163" s="4"/>
       <c r="C163" s="4"/>
@@ -4471,7 +4011,7 @@
       <c r="H163" s="4"/>
       <c r="I163" s="4"/>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A164" s="4"/>
       <c r="B164" s="4"/>
       <c r="C164" s="4"/>
@@ -4482,7 +4022,7 @@
       <c r="H164" s="4"/>
       <c r="I164" s="4"/>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A165" s="4"/>
       <c r="B165" s="4"/>
       <c r="C165" s="4"/>
@@ -4493,7 +4033,7 @@
       <c r="H165" s="4"/>
       <c r="I165" s="4"/>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A166" s="4"/>
       <c r="B166" s="4"/>
       <c r="C166" s="4"/>
@@ -4504,7 +4044,7 @@
       <c r="H166" s="4"/>
       <c r="I166" s="4"/>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A167" s="4"/>
       <c r="B167" s="4"/>
       <c r="C167" s="4"/>
@@ -4515,7 +4055,7 @@
       <c r="H167" s="4"/>
       <c r="I167" s="4"/>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A168" s="4"/>
       <c r="B168" s="4"/>
       <c r="C168" s="4"/>
@@ -4526,7 +4066,7 @@
       <c r="H168" s="4"/>
       <c r="I168" s="4"/>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A169" s="4"/>
       <c r="B169" s="4"/>
       <c r="C169" s="4"/>
@@ -4537,7 +4077,7 @@
       <c r="H169" s="4"/>
       <c r="I169" s="4"/>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A170" s="4"/>
       <c r="B170" s="4"/>
       <c r="C170" s="4"/>
@@ -4548,7 +4088,7 @@
       <c r="H170" s="4"/>
       <c r="I170" s="4"/>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A171" s="4"/>
       <c r="B171" s="4"/>
       <c r="C171" s="4"/>
@@ -4559,7 +4099,7 @@
       <c r="H171" s="4"/>
       <c r="I171" s="4"/>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A172" s="4"/>
       <c r="B172" s="4"/>
       <c r="C172" s="4"/>
@@ -4570,7 +4110,7 @@
       <c r="H172" s="4"/>
       <c r="I172" s="4"/>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A173" s="4"/>
       <c r="B173" s="4"/>
       <c r="C173" s="4"/>
@@ -4581,7 +4121,7 @@
       <c r="H173" s="4"/>
       <c r="I173" s="4"/>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A174" s="4"/>
       <c r="B174" s="4"/>
       <c r="C174" s="4"/>
@@ -4592,7 +4132,7 @@
       <c r="H174" s="4"/>
       <c r="I174" s="4"/>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A175" s="4"/>
       <c r="B175" s="4"/>
       <c r="C175" s="4"/>
@@ -4603,7 +4143,7 @@
       <c r="H175" s="4"/>
       <c r="I175" s="4"/>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A176" s="4"/>
       <c r="B176" s="4"/>
       <c r="C176" s="4"/>
@@ -4614,7 +4154,7 @@
       <c r="H176" s="4"/>
       <c r="I176" s="4"/>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A177" s="4"/>
       <c r="B177" s="4"/>
       <c r="C177" s="4"/>
@@ -4625,7 +4165,7 @@
       <c r="H177" s="4"/>
       <c r="I177" s="4"/>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A178" s="4"/>
       <c r="B178" s="4"/>
       <c r="C178" s="4"/>
@@ -4636,7 +4176,7 @@
       <c r="H178" s="4"/>
       <c r="I178" s="4"/>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A179" s="4"/>
       <c r="B179" s="4"/>
       <c r="C179" s="4"/>
@@ -4647,7 +4187,7 @@
       <c r="H179" s="4"/>
       <c r="I179" s="4"/>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A180" s="4"/>
       <c r="B180" s="4"/>
       <c r="C180" s="4"/>
@@ -4658,7 +4198,7 @@
       <c r="H180" s="4"/>
       <c r="I180" s="4"/>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A181" s="4"/>
       <c r="B181" s="4"/>
       <c r="C181" s="4"/>
@@ -4669,7 +4209,7 @@
       <c r="H181" s="4"/>
       <c r="I181" s="4"/>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A182" s="4"/>
       <c r="B182" s="4"/>
       <c r="C182" s="4"/>
@@ -4680,7 +4220,7 @@
       <c r="H182" s="4"/>
       <c r="I182" s="4"/>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A183" s="4"/>
       <c r="B183" s="4"/>
       <c r="C183" s="4"/>
@@ -4691,7 +4231,7 @@
       <c r="H183" s="4"/>
       <c r="I183" s="4"/>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A184" s="4"/>
       <c r="B184" s="4"/>
       <c r="C184" s="4"/>
@@ -4702,7 +4242,7 @@
       <c r="H184" s="4"/>
       <c r="I184" s="4"/>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A185" s="4"/>
       <c r="B185" s="4"/>
       <c r="C185" s="4"/>
@@ -4713,7 +4253,7 @@
       <c r="H185" s="4"/>
       <c r="I185" s="4"/>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A186" s="4"/>
       <c r="B186" s="4"/>
       <c r="C186" s="4"/>
@@ -4724,7 +4264,7 @@
       <c r="H186" s="4"/>
       <c r="I186" s="4"/>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A187" s="4"/>
       <c r="B187" s="4"/>
       <c r="C187" s="4"/>
@@ -4735,7 +4275,7 @@
       <c r="H187" s="4"/>
       <c r="I187" s="4"/>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A188" s="4"/>
       <c r="B188" s="4"/>
       <c r="C188" s="4"/>
@@ -4746,7 +4286,7 @@
       <c r="H188" s="4"/>
       <c r="I188" s="4"/>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A189" s="4"/>
       <c r="B189" s="4"/>
       <c r="C189" s="4"/>
@@ -4757,7 +4297,7 @@
       <c r="H189" s="4"/>
       <c r="I189" s="4"/>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A190" s="4"/>
       <c r="B190" s="4"/>
       <c r="C190" s="4"/>
@@ -4768,7 +4308,7 @@
       <c r="H190" s="4"/>
       <c r="I190" s="4"/>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A191" s="4"/>
       <c r="B191" s="4"/>
       <c r="C191" s="4"/>
@@ -4779,7 +4319,7 @@
       <c r="H191" s="4"/>
       <c r="I191" s="4"/>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A192" s="4"/>
       <c r="B192" s="4"/>
       <c r="C192" s="4"/>
@@ -4790,7 +4330,7 @@
       <c r="H192" s="4"/>
       <c r="I192" s="4"/>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A193" s="4"/>
       <c r="B193" s="4"/>
       <c r="C193" s="4"/>
@@ -4801,7 +4341,7 @@
       <c r="H193" s="4"/>
       <c r="I193" s="4"/>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A194" s="4"/>
       <c r="B194" s="4"/>
       <c r="C194" s="4"/>
@@ -4812,7 +4352,7 @@
       <c r="H194" s="4"/>
       <c r="I194" s="4"/>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A195" s="4"/>
       <c r="B195" s="4"/>
       <c r="C195" s="4"/>
@@ -4823,7 +4363,7 @@
       <c r="H195" s="4"/>
       <c r="I195" s="4"/>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A196" s="4"/>
       <c r="B196" s="4"/>
       <c r="C196" s="4"/>
@@ -4834,7 +4374,7 @@
       <c r="H196" s="4"/>
       <c r="I196" s="4"/>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A197" s="4"/>
       <c r="B197" s="4"/>
       <c r="C197" s="4"/>
@@ -4845,7 +4385,7 @@
       <c r="H197" s="4"/>
       <c r="I197" s="4"/>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A198" s="4"/>
       <c r="B198" s="4"/>
       <c r="C198" s="4"/>
@@ -4856,7 +4396,7 @@
       <c r="H198" s="4"/>
       <c r="I198" s="4"/>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A199" s="4"/>
       <c r="B199" s="4"/>
       <c r="C199" s="4"/>
@@ -4867,7 +4407,7 @@
       <c r="H199" s="4"/>
       <c r="I199" s="4"/>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A200" s="4"/>
       <c r="B200" s="4"/>
       <c r="C200" s="4"/>
@@ -4878,7 +4418,7 @@
       <c r="H200" s="4"/>
       <c r="I200" s="4"/>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A201" s="4"/>
       <c r="B201" s="4"/>
       <c r="C201" s="4"/>
@@ -4889,7 +4429,7 @@
       <c r="H201" s="4"/>
       <c r="I201" s="4"/>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A202" s="4"/>
       <c r="B202" s="4"/>
       <c r="C202" s="4"/>
@@ -4900,7 +4440,7 @@
       <c r="H202" s="4"/>
       <c r="I202" s="4"/>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A203" s="4"/>
       <c r="B203" s="4"/>
       <c r="C203" s="4"/>
@@ -4911,7 +4451,7 @@
       <c r="H203" s="4"/>
       <c r="I203" s="4"/>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A204" s="4"/>
       <c r="B204" s="4"/>
       <c r="C204" s="4"/>
@@ -4922,7 +4462,7 @@
       <c r="H204" s="4"/>
       <c r="I204" s="4"/>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A205" s="4"/>
       <c r="B205" s="4"/>
       <c r="C205" s="4"/>
@@ -4933,7 +4473,7 @@
       <c r="H205" s="4"/>
       <c r="I205" s="4"/>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A206" s="4"/>
       <c r="B206" s="4"/>
       <c r="C206" s="4"/>
@@ -4944,7 +4484,7 @@
       <c r="H206" s="4"/>
       <c r="I206" s="4"/>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A207" s="4"/>
       <c r="B207" s="4"/>
       <c r="C207" s="4"/>
@@ -4955,7 +4495,7 @@
       <c r="H207" s="4"/>
       <c r="I207" s="4"/>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A208" s="4"/>
       <c r="B208" s="4"/>
       <c r="C208" s="4"/>
@@ -4966,7 +4506,7 @@
       <c r="H208" s="4"/>
       <c r="I208" s="4"/>
     </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A209" s="4"/>
       <c r="B209" s="4"/>
       <c r="C209" s="4"/>
@@ -4977,7 +4517,7 @@
       <c r="H209" s="4"/>
       <c r="I209" s="4"/>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A210" s="4"/>
       <c r="B210" s="4"/>
       <c r="C210" s="4"/>
@@ -4988,7 +4528,7 @@
       <c r="H210" s="4"/>
       <c r="I210" s="4"/>
     </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A211" s="4"/>
       <c r="B211" s="4"/>
       <c r="C211" s="4"/>
@@ -4999,7 +4539,7 @@
       <c r="H211" s="4"/>
       <c r="I211" s="4"/>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A212" s="4"/>
       <c r="B212" s="4"/>
       <c r="C212" s="4"/>
@@ -5010,7 +4550,7 @@
       <c r="H212" s="4"/>
       <c r="I212" s="4"/>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A213" s="4"/>
       <c r="B213" s="4"/>
       <c r="C213" s="4"/>
@@ -5021,7 +4561,7 @@
       <c r="H213" s="4"/>
       <c r="I213" s="4"/>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A214" s="4"/>
       <c r="B214" s="4"/>
       <c r="C214" s="4"/>
@@ -5032,7 +4572,7 @@
       <c r="H214" s="4"/>
       <c r="I214" s="4"/>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A215" s="4"/>
       <c r="B215" s="4"/>
       <c r="C215" s="4"/>
@@ -5043,7 +4583,7 @@
       <c r="H215" s="4"/>
       <c r="I215" s="4"/>
     </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A216" s="4"/>
       <c r="B216" s="4"/>
       <c r="C216" s="4"/>
@@ -5054,7 +4594,7 @@
       <c r="H216" s="4"/>
       <c r="I216" s="4"/>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A217" s="4"/>
       <c r="B217" s="4"/>
       <c r="C217" s="4"/>
@@ -5065,7 +4605,7 @@
       <c r="H217" s="4"/>
       <c r="I217" s="4"/>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A218" s="4"/>
       <c r="B218" s="4"/>
       <c r="C218" s="4"/>
@@ -5076,7 +4616,7 @@
       <c r="H218" s="4"/>
       <c r="I218" s="4"/>
     </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A219" s="4"/>
       <c r="B219" s="4"/>
       <c r="C219" s="4"/>
@@ -5087,7 +4627,7 @@
       <c r="H219" s="4"/>
       <c r="I219" s="4"/>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A220" s="4"/>
       <c r="B220" s="4"/>
       <c r="C220" s="4"/>
@@ -5098,7 +4638,7 @@
       <c r="H220" s="4"/>
       <c r="I220" s="4"/>
     </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A221" s="4"/>
       <c r="B221" s="4"/>
       <c r="C221" s="4"/>
@@ -5109,7 +4649,7 @@
       <c r="H221" s="4"/>
       <c r="I221" s="4"/>
     </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A222" s="4"/>
       <c r="B222" s="4"/>
       <c r="C222" s="4"/>
@@ -5120,7 +4660,7 @@
       <c r="H222" s="4"/>
       <c r="I222" s="4"/>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A223" s="4"/>
       <c r="B223" s="4"/>
       <c r="C223" s="4"/>
@@ -5131,7 +4671,7 @@
       <c r="H223" s="4"/>
       <c r="I223" s="4"/>
     </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A224" s="4"/>
       <c r="B224" s="4"/>
       <c r="C224" s="4"/>
@@ -5142,7 +4682,7 @@
       <c r="H224" s="4"/>
       <c r="I224" s="4"/>
     </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A225" s="4"/>
       <c r="B225" s="4"/>
       <c r="C225" s="4"/>
@@ -5153,7 +4693,7 @@
       <c r="H225" s="4"/>
       <c r="I225" s="4"/>
     </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A226" s="4"/>
       <c r="B226" s="4"/>
       <c r="C226" s="4"/>
@@ -5164,7 +4704,7 @@
       <c r="H226" s="4"/>
       <c r="I226" s="4"/>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A227" s="4"/>
       <c r="B227" s="4"/>
       <c r="C227" s="4"/>
@@ -5175,7 +4715,7 @@
       <c r="H227" s="4"/>
       <c r="I227" s="4"/>
     </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A228" s="4"/>
       <c r="B228" s="4"/>
       <c r="C228" s="4"/>
@@ -5186,7 +4726,7 @@
       <c r="H228" s="4"/>
       <c r="I228" s="4"/>
     </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A229" s="4"/>
       <c r="B229" s="4"/>
       <c r="C229" s="4"/>
@@ -5197,7 +4737,7 @@
       <c r="H229" s="4"/>
       <c r="I229" s="4"/>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A230" s="4"/>
       <c r="B230" s="4"/>
       <c r="C230" s="4"/>
@@ -5208,7 +4748,7 @@
       <c r="H230" s="4"/>
       <c r="I230" s="4"/>
     </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A231" s="4"/>
       <c r="B231" s="4"/>
       <c r="C231" s="4"/>
@@ -5219,7 +4759,7 @@
       <c r="H231" s="4"/>
       <c r="I231" s="4"/>
     </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A232" s="4"/>
       <c r="B232" s="4"/>
       <c r="C232" s="4"/>
@@ -5230,7 +4770,7 @@
       <c r="H232" s="4"/>
       <c r="I232" s="4"/>
     </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A233" s="4"/>
       <c r="B233" s="4"/>
       <c r="C233" s="4"/>
@@ -5241,7 +4781,7 @@
       <c r="H233" s="4"/>
       <c r="I233" s="4"/>
     </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A234" s="4"/>
       <c r="B234" s="4"/>
       <c r="C234" s="4"/>
@@ -5252,7 +4792,7 @@
       <c r="H234" s="4"/>
       <c r="I234" s="4"/>
     </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A235" s="4"/>
       <c r="B235" s="4"/>
       <c r="C235" s="4"/>
@@ -5263,7 +4803,7 @@
       <c r="H235" s="4"/>
       <c r="I235" s="4"/>
     </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A236" s="4"/>
       <c r="B236" s="4"/>
       <c r="C236" s="4"/>
@@ -5274,7 +4814,7 @@
       <c r="H236" s="4"/>
       <c r="I236" s="4"/>
     </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A237" s="4"/>
       <c r="B237" s="4"/>
       <c r="C237" s="4"/>
@@ -5285,7 +4825,7 @@
       <c r="H237" s="4"/>
       <c r="I237" s="4"/>
     </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A238" s="4"/>
       <c r="B238" s="4"/>
       <c r="C238" s="4"/>
@@ -5296,7 +4836,7 @@
       <c r="H238" s="4"/>
       <c r="I238" s="4"/>
     </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A239" s="4"/>
       <c r="B239" s="4"/>
       <c r="C239" s="4"/>
@@ -5307,7 +4847,7 @@
       <c r="H239" s="4"/>
       <c r="I239" s="4"/>
     </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A240" s="4"/>
       <c r="B240" s="4"/>
       <c r="C240" s="4"/>
@@ -5318,7 +4858,7 @@
       <c r="H240" s="4"/>
       <c r="I240" s="4"/>
     </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A241" s="4"/>
       <c r="B241" s="4"/>
       <c r="C241" s="4"/>
@@ -5329,7 +4869,7 @@
       <c r="H241" s="4"/>
       <c r="I241" s="4"/>
     </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A242" s="4"/>
       <c r="B242" s="4"/>
       <c r="C242" s="4"/>
@@ -5340,7 +4880,7 @@
       <c r="H242" s="4"/>
       <c r="I242" s="4"/>
     </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A243" s="4"/>
       <c r="B243" s="4"/>
       <c r="C243" s="4"/>
@@ -5351,7 +4891,7 @@
       <c r="H243" s="4"/>
       <c r="I243" s="4"/>
     </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A244" s="4"/>
       <c r="B244" s="4"/>
       <c r="C244" s="4"/>
@@ -5362,7 +4902,7 @@
       <c r="H244" s="4"/>
       <c r="I244" s="4"/>
     </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A245" s="4"/>
       <c r="B245" s="4"/>
       <c r="C245" s="4"/>
@@ -5373,7 +4913,7 @@
       <c r="H245" s="4"/>
       <c r="I245" s="4"/>
     </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A246" s="4"/>
       <c r="B246" s="4"/>
       <c r="C246" s="4"/>
@@ -5384,7 +4924,7 @@
       <c r="H246" s="4"/>
       <c r="I246" s="4"/>
     </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A247" s="4"/>
       <c r="B247" s="4"/>
       <c r="C247" s="4"/>
@@ -5395,7 +4935,7 @@
       <c r="H247" s="4"/>
       <c r="I247" s="4"/>
     </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A248" s="4"/>
       <c r="B248" s="4"/>
       <c r="C248" s="4"/>
@@ -5406,7 +4946,7 @@
       <c r="H248" s="4"/>
       <c r="I248" s="4"/>
     </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A249" s="4"/>
       <c r="B249" s="4"/>
       <c r="C249" s="4"/>
@@ -5417,7 +4957,7 @@
       <c r="H249" s="4"/>
       <c r="I249" s="4"/>
     </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A250" s="4"/>
       <c r="B250" s="4"/>
       <c r="C250" s="4"/>
@@ -5428,7 +4968,7 @@
       <c r="H250" s="4"/>
       <c r="I250" s="4"/>
     </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A251" s="4"/>
       <c r="B251" s="4"/>
       <c r="C251" s="4"/>
@@ -5439,7 +4979,7 @@
       <c r="H251" s="4"/>
       <c r="I251" s="4"/>
     </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A252" s="4"/>
       <c r="B252" s="4"/>
       <c r="C252" s="4"/>
@@ -5450,7 +4990,7 @@
       <c r="H252" s="4"/>
       <c r="I252" s="4"/>
     </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A253" s="4"/>
       <c r="B253" s="4"/>
       <c r="C253" s="4"/>
@@ -5461,7 +5001,7 @@
       <c r="H253" s="4"/>
       <c r="I253" s="4"/>
     </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A254" s="4"/>
       <c r="B254" s="4"/>
       <c r="C254" s="4"/>
@@ -5472,7 +5012,7 @@
       <c r="H254" s="4"/>
       <c r="I254" s="4"/>
     </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A255" s="4"/>
       <c r="B255" s="4"/>
       <c r="C255" s="4"/>
@@ -5483,7 +5023,7 @@
       <c r="H255" s="4"/>
       <c r="I255" s="4"/>
     </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A256" s="4"/>
       <c r="B256" s="4"/>
       <c r="C256" s="4"/>
@@ -5494,7 +5034,7 @@
       <c r="H256" s="4"/>
       <c r="I256" s="4"/>
     </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A257" s="4"/>
       <c r="B257" s="4"/>
       <c r="C257" s="4"/>
@@ -5505,7 +5045,7 @@
       <c r="H257" s="4"/>
       <c r="I257" s="4"/>
     </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A258" s="4"/>
       <c r="B258" s="4"/>
       <c r="C258" s="4"/>
@@ -5516,7 +5056,7 @@
       <c r="H258" s="4"/>
       <c r="I258" s="4"/>
     </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A259" s="4"/>
       <c r="B259" s="4"/>
       <c r="C259" s="4"/>
@@ -5527,7 +5067,7 @@
       <c r="H259" s="4"/>
       <c r="I259" s="4"/>
     </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A260" s="4"/>
       <c r="B260" s="4"/>
       <c r="C260" s="4"/>
@@ -5538,7 +5078,7 @@
       <c r="H260" s="4"/>
       <c r="I260" s="4"/>
     </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A261" s="4"/>
       <c r="B261" s="4"/>
       <c r="C261" s="4"/>
@@ -5549,7 +5089,7 @@
       <c r="H261" s="4"/>
       <c r="I261" s="4"/>
     </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A262" s="4"/>
       <c r="B262" s="4"/>
       <c r="C262" s="4"/>
@@ -5560,7 +5100,7 @@
       <c r="H262" s="4"/>
       <c r="I262" s="4"/>
     </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A263" s="4"/>
       <c r="B263" s="4"/>
       <c r="C263" s="4"/>
@@ -5571,7 +5111,7 @@
       <c r="H263" s="4"/>
       <c r="I263" s="4"/>
     </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A264" s="4"/>
       <c r="B264" s="4"/>
       <c r="C264" s="4"/>
@@ -5582,7 +5122,7 @@
       <c r="H264" s="4"/>
       <c r="I264" s="4"/>
     </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A265" s="4"/>
       <c r="B265" s="4"/>
       <c r="C265" s="4"/>
@@ -5593,7 +5133,7 @@
       <c r="H265" s="4"/>
       <c r="I265" s="4"/>
     </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A266" s="4"/>
       <c r="B266" s="4"/>
       <c r="C266" s="4"/>
@@ -5604,7 +5144,7 @@
       <c r="H266" s="4"/>
       <c r="I266" s="4"/>
     </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A267" s="4"/>
       <c r="B267" s="4"/>
       <c r="C267" s="4"/>
@@ -5615,7 +5155,7 @@
       <c r="H267" s="4"/>
       <c r="I267" s="4"/>
     </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A268" s="4"/>
       <c r="B268" s="4"/>
       <c r="C268" s="4"/>
@@ -5626,7 +5166,7 @@
       <c r="H268" s="4"/>
       <c r="I268" s="4"/>
     </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A269" s="4"/>
       <c r="B269" s="4"/>
       <c r="C269" s="4"/>
@@ -5637,7 +5177,7 @@
       <c r="H269" s="4"/>
       <c r="I269" s="4"/>
     </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A270" s="4"/>
       <c r="B270" s="4"/>
       <c r="C270" s="4"/>
@@ -5648,7 +5188,7 @@
       <c r="H270" s="4"/>
       <c r="I270" s="4"/>
     </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A271" s="4"/>
       <c r="B271" s="4"/>
       <c r="C271" s="4"/>
@@ -5659,7 +5199,7 @@
       <c r="H271" s="4"/>
       <c r="I271" s="4"/>
     </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A272" s="4"/>
       <c r="B272" s="4"/>
       <c r="C272" s="4"/>
@@ -5670,7 +5210,7 @@
       <c r="H272" s="4"/>
       <c r="I272" s="4"/>
     </row>
-    <row r="273" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A273" s="4"/>
       <c r="B273" s="4"/>
       <c r="C273" s="4"/>
@@ -5681,7 +5221,7 @@
       <c r="H273" s="4"/>
       <c r="I273" s="4"/>
     </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A274" s="4"/>
       <c r="B274" s="4"/>
       <c r="C274" s="4"/>
@@ -5692,7 +5232,7 @@
       <c r="H274" s="4"/>
       <c r="I274" s="4"/>
     </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A275" s="4"/>
       <c r="B275" s="4"/>
       <c r="C275" s="4"/>
@@ -5703,7 +5243,7 @@
       <c r="H275" s="4"/>
       <c r="I275" s="4"/>
     </row>
-    <row r="276" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A276" s="4"/>
       <c r="B276" s="4"/>
       <c r="C276" s="4"/>
@@ -5714,7 +5254,7 @@
       <c r="H276" s="4"/>
       <c r="I276" s="4"/>
     </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A277" s="4"/>
       <c r="B277" s="4"/>
       <c r="C277" s="4"/>
@@ -5725,7 +5265,7 @@
       <c r="H277" s="4"/>
       <c r="I277" s="4"/>
     </row>
-    <row r="278" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A278" s="4"/>
       <c r="B278" s="4"/>
       <c r="C278" s="4"/>
@@ -5736,7 +5276,7 @@
       <c r="H278" s="4"/>
       <c r="I278" s="4"/>
     </row>
-    <row r="279" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A279" s="4"/>
       <c r="B279" s="4"/>
       <c r="C279" s="4"/>
@@ -5747,7 +5287,7 @@
       <c r="H279" s="4"/>
       <c r="I279" s="4"/>
     </row>
-    <row r="280" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A280" s="4"/>
       <c r="B280" s="4"/>
       <c r="C280" s="4"/>
@@ -5758,7 +5298,7 @@
       <c r="H280" s="4"/>
       <c r="I280" s="4"/>
     </row>
-    <row r="281" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A281" s="4"/>
       <c r="B281" s="4"/>
       <c r="C281" s="4"/>
@@ -5769,7 +5309,7 @@
       <c r="H281" s="4"/>
       <c r="I281" s="4"/>
     </row>
-    <row r="282" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A282" s="4"/>
       <c r="B282" s="4"/>
       <c r="C282" s="4"/>
@@ -5780,7 +5320,7 @@
       <c r="H282" s="4"/>
       <c r="I282" s="4"/>
     </row>
-    <row r="283" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A283" s="4"/>
       <c r="B283" s="4"/>
       <c r="C283" s="4"/>
@@ -5791,7 +5331,7 @@
       <c r="H283" s="4"/>
       <c r="I283" s="4"/>
     </row>
-    <row r="284" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A284" s="4"/>
       <c r="B284" s="4"/>
       <c r="C284" s="4"/>
@@ -5802,7 +5342,7 @@
       <c r="H284" s="4"/>
       <c r="I284" s="4"/>
     </row>
-    <row r="285" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A285" s="4"/>
       <c r="B285" s="4"/>
       <c r="C285" s="4"/>
@@ -5813,7 +5353,7 @@
       <c r="H285" s="4"/>
       <c r="I285" s="4"/>
     </row>
-    <row r="286" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A286" s="4"/>
       <c r="B286" s="4"/>
       <c r="C286" s="4"/>
@@ -5824,7 +5364,7 @@
       <c r="H286" s="4"/>
       <c r="I286" s="4"/>
     </row>
-    <row r="287" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A287" s="4"/>
       <c r="B287" s="4"/>
       <c r="C287" s="4"/>
@@ -5835,7 +5375,7 @@
       <c r="H287" s="4"/>
       <c r="I287" s="4"/>
     </row>
-    <row r="288" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A288" s="4"/>
       <c r="B288" s="4"/>
       <c r="C288" s="4"/>
@@ -5846,7 +5386,7 @@
       <c r="H288" s="4"/>
       <c r="I288" s="4"/>
     </row>
-    <row r="289" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A289" s="4"/>
       <c r="B289" s="4"/>
       <c r="C289" s="4"/>
@@ -5857,7 +5397,7 @@
       <c r="H289" s="4"/>
       <c r="I289" s="4"/>
     </row>
-    <row r="290" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A290" s="4"/>
       <c r="B290" s="4"/>
       <c r="C290" s="4"/>
@@ -5868,7 +5408,7 @@
       <c r="H290" s="4"/>
       <c r="I290" s="4"/>
     </row>
-    <row r="291" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A291" s="4"/>
       <c r="B291" s="4"/>
       <c r="C291" s="4"/>
@@ -5879,7 +5419,7 @@
       <c r="H291" s="4"/>
       <c r="I291" s="4"/>
     </row>
-    <row r="292" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A292" s="4"/>
       <c r="B292" s="4"/>
       <c r="C292" s="4"/>
@@ -5890,7 +5430,7 @@
       <c r="H292" s="4"/>
       <c r="I292" s="4"/>
     </row>
-    <row r="293" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A293" s="4"/>
       <c r="B293" s="4"/>
       <c r="C293" s="4"/>
@@ -5901,7 +5441,7 @@
       <c r="H293" s="4"/>
       <c r="I293" s="4"/>
     </row>
-    <row r="294" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A294" s="4"/>
       <c r="B294" s="4"/>
       <c r="C294" s="4"/>
@@ -5912,7 +5452,7 @@
       <c r="H294" s="4"/>
       <c r="I294" s="4"/>
     </row>
-    <row r="295" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A295" s="4"/>
       <c r="B295" s="4"/>
       <c r="C295" s="4"/>
@@ -5923,7 +5463,7 @@
       <c r="H295" s="4"/>
       <c r="I295" s="4"/>
     </row>
-    <row r="296" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A296" s="4"/>
       <c r="B296" s="4"/>
       <c r="C296" s="4"/>
@@ -5934,7 +5474,7 @@
       <c r="H296" s="4"/>
       <c r="I296" s="4"/>
     </row>
-    <row r="297" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A297" s="4"/>
       <c r="B297" s="4"/>
       <c r="C297" s="4"/>
@@ -5945,7 +5485,7 @@
       <c r="H297" s="4"/>
       <c r="I297" s="4"/>
     </row>
-    <row r="298" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A298" s="4"/>
       <c r="B298" s="4"/>
       <c r="C298" s="4"/>
@@ -5956,7 +5496,7 @@
       <c r="H298" s="4"/>
       <c r="I298" s="4"/>
     </row>
-    <row r="299" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A299" s="4"/>
       <c r="B299" s="4"/>
       <c r="C299" s="4"/>
@@ -5967,7 +5507,7 @@
       <c r="H299" s="4"/>
       <c r="I299" s="4"/>
     </row>
-    <row r="300" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A300" s="4"/>
       <c r="B300" s="4"/>
       <c r="C300" s="4"/>
@@ -5978,7 +5518,7 @@
       <c r="H300" s="4"/>
       <c r="I300" s="4"/>
     </row>
-    <row r="301" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A301" s="4"/>
       <c r="B301" s="4"/>
       <c r="C301" s="4"/>
@@ -5989,7 +5529,7 @@
       <c r="H301" s="4"/>
       <c r="I301" s="4"/>
     </row>
-    <row r="302" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A302" s="4"/>
       <c r="B302" s="4"/>
       <c r="C302" s="4"/>
@@ -6000,7 +5540,7 @@
       <c r="H302" s="4"/>
       <c r="I302" s="4"/>
     </row>
-    <row r="303" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A303" s="4"/>
       <c r="B303" s="4"/>
       <c r="C303" s="4"/>
@@ -6011,7 +5551,7 @@
       <c r="H303" s="4"/>
       <c r="I303" s="4"/>
     </row>
-    <row r="304" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A304" s="4"/>
       <c r="B304" s="4"/>
       <c r="C304" s="4"/>
@@ -6022,7 +5562,7 @@
       <c r="H304" s="4"/>
       <c r="I304" s="4"/>
     </row>
-    <row r="305" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A305" s="4"/>
       <c r="B305" s="4"/>
       <c r="C305" s="4"/>
@@ -6033,7 +5573,7 @@
       <c r="H305" s="4"/>
       <c r="I305" s="4"/>
     </row>
-    <row r="306" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A306" s="4"/>
       <c r="B306" s="4"/>
       <c r="C306" s="4"/>
@@ -6044,7 +5584,7 @@
       <c r="H306" s="4"/>
       <c r="I306" s="4"/>
     </row>
-    <row r="307" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A307" s="4"/>
       <c r="B307" s="4"/>
       <c r="C307" s="4"/>
@@ -6055,7 +5595,7 @@
       <c r="H307" s="4"/>
       <c r="I307" s="4"/>
     </row>
-    <row r="308" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A308" s="4"/>
       <c r="B308" s="4"/>
       <c r="C308" s="4"/>
@@ -6066,7 +5606,7 @@
       <c r="H308" s="4"/>
       <c r="I308" s="4"/>
     </row>
-    <row r="309" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A309" s="4"/>
       <c r="B309" s="4"/>
       <c r="C309" s="4"/>
@@ -6077,7 +5617,7 @@
       <c r="H309" s="4"/>
       <c r="I309" s="4"/>
     </row>
-    <row r="310" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A310" s="4"/>
       <c r="B310" s="4"/>
       <c r="C310" s="4"/>
@@ -6088,7 +5628,7 @@
       <c r="H310" s="4"/>
       <c r="I310" s="4"/>
     </row>
-    <row r="311" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A311" s="4"/>
       <c r="B311" s="4"/>
       <c r="C311" s="4"/>
@@ -6099,7 +5639,7 @@
       <c r="H311" s="4"/>
       <c r="I311" s="4"/>
     </row>
-    <row r="312" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A312" s="4"/>
       <c r="B312" s="4"/>
       <c r="C312" s="4"/>
@@ -6110,7 +5650,7 @@
       <c r="H312" s="4"/>
       <c r="I312" s="4"/>
     </row>
-    <row r="313" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A313" s="4"/>
       <c r="B313" s="4"/>
       <c r="C313" s="4"/>
@@ -6121,7 +5661,7 @@
       <c r="H313" s="4"/>
       <c r="I313" s="4"/>
     </row>
-    <row r="314" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A314" s="4"/>
       <c r="B314" s="4"/>
       <c r="C314" s="4"/>
@@ -6132,7 +5672,7 @@
       <c r="H314" s="4"/>
       <c r="I314" s="4"/>
     </row>
-    <row r="315" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A315" s="4"/>
       <c r="B315" s="4"/>
       <c r="C315" s="4"/>
@@ -6143,7 +5683,7 @@
       <c r="H315" s="4"/>
       <c r="I315" s="4"/>
     </row>
-    <row r="316" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A316" s="4"/>
       <c r="B316" s="4"/>
       <c r="C316" s="4"/>
@@ -6154,7 +5694,7 @@
       <c r="H316" s="4"/>
       <c r="I316" s="4"/>
     </row>
-    <row r="317" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A317" s="4"/>
       <c r="B317" s="4"/>
       <c r="C317" s="4"/>
@@ -6165,7 +5705,7 @@
       <c r="H317" s="4"/>
       <c r="I317" s="4"/>
     </row>
-    <row r="318" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A318" s="4"/>
       <c r="B318" s="4"/>
       <c r="C318" s="4"/>
@@ -6176,7 +5716,7 @@
       <c r="H318" s="4"/>
       <c r="I318" s="4"/>
     </row>
-    <row r="319" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A319" s="4"/>
       <c r="B319" s="4"/>
       <c r="C319" s="4"/>
@@ -6187,7 +5727,7 @@
       <c r="H319" s="4"/>
       <c r="I319" s="4"/>
     </row>
-    <row r="320" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A320" s="4"/>
       <c r="B320" s="4"/>
       <c r="C320" s="4"/>
@@ -6198,7 +5738,7 @@
       <c r="H320" s="4"/>
       <c r="I320" s="4"/>
     </row>
-    <row r="321" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A321" s="4"/>
       <c r="B321" s="4"/>
       <c r="C321" s="4"/>
@@ -6209,7 +5749,7 @@
       <c r="H321" s="4"/>
       <c r="I321" s="4"/>
     </row>
-    <row r="322" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A322" s="4"/>
       <c r="B322" s="4"/>
       <c r="C322" s="4"/>
@@ -6220,7 +5760,7 @@
       <c r="H322" s="4"/>
       <c r="I322" s="4"/>
     </row>
-    <row r="323" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A323" s="4"/>
       <c r="B323" s="4"/>
       <c r="C323" s="4"/>
@@ -6231,7 +5771,7 @@
       <c r="H323" s="4"/>
       <c r="I323" s="4"/>
     </row>
-    <row r="324" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A324" s="4"/>
       <c r="B324" s="4"/>
       <c r="C324" s="4"/>
@@ -6242,7 +5782,7 @@
       <c r="H324" s="4"/>
       <c r="I324" s="4"/>
     </row>
-    <row r="325" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A325" s="4"/>
       <c r="B325" s="4"/>
       <c r="C325" s="4"/>
@@ -6253,7 +5793,7 @@
       <c r="H325" s="4"/>
       <c r="I325" s="4"/>
     </row>
-    <row r="326" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A326" s="4"/>
       <c r="B326" s="4"/>
       <c r="C326" s="4"/>
@@ -6264,7 +5804,7 @@
       <c r="H326" s="4"/>
       <c r="I326" s="4"/>
     </row>
-    <row r="327" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A327" s="4"/>
       <c r="B327" s="4"/>
       <c r="C327" s="4"/>
@@ -6275,7 +5815,7 @@
       <c r="H327" s="4"/>
       <c r="I327" s="4"/>
     </row>
-    <row r="328" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A328" s="4"/>
       <c r="B328" s="4"/>
       <c r="C328" s="4"/>
@@ -6286,7 +5826,7 @@
       <c r="H328" s="4"/>
       <c r="I328" s="4"/>
     </row>
-    <row r="329" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A329" s="4"/>
       <c r="B329" s="4"/>
       <c r="C329" s="4"/>
@@ -6297,7 +5837,7 @@
       <c r="H329" s="4"/>
       <c r="I329" s="4"/>
     </row>
-    <row r="330" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A330" s="4"/>
       <c r="B330" s="4"/>
       <c r="C330" s="4"/>
@@ -6308,7 +5848,7 @@
       <c r="H330" s="4"/>
       <c r="I330" s="4"/>
     </row>
-    <row r="331" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A331" s="4"/>
       <c r="B331" s="4"/>
       <c r="C331" s="4"/>
@@ -6319,7 +5859,7 @@
       <c r="H331" s="4"/>
       <c r="I331" s="4"/>
     </row>
-    <row r="332" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A332" s="4"/>
       <c r="B332" s="4"/>
       <c r="C332" s="4"/>
@@ -6330,7 +5870,7 @@
       <c r="H332" s="4"/>
       <c r="I332" s="4"/>
     </row>
-    <row r="333" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A333" s="4"/>
       <c r="B333" s="4"/>
       <c r="C333" s="4"/>
@@ -6341,7 +5881,7 @@
       <c r="H333" s="4"/>
       <c r="I333" s="4"/>
     </row>
-    <row r="334" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A334" s="4"/>
       <c r="B334" s="4"/>
       <c r="C334" s="4"/>
@@ -6352,7 +5892,7 @@
       <c r="H334" s="4"/>
       <c r="I334" s="4"/>
     </row>
-    <row r="335" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A335" s="4"/>
       <c r="B335" s="4"/>
       <c r="C335" s="4"/>
@@ -6363,7 +5903,7 @@
       <c r="H335" s="4"/>
       <c r="I335" s="4"/>
     </row>
-    <row r="336" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A336" s="4"/>
       <c r="B336" s="4"/>
       <c r="C336" s="4"/>
@@ -6374,7 +5914,7 @@
       <c r="H336" s="4"/>
       <c r="I336" s="4"/>
     </row>
-    <row r="337" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A337" s="4"/>
       <c r="B337" s="4"/>
       <c r="C337" s="4"/>
@@ -6385,7 +5925,7 @@
       <c r="H337" s="4"/>
       <c r="I337" s="4"/>
     </row>
-    <row r="338" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A338" s="4"/>
       <c r="B338" s="4"/>
       <c r="C338" s="4"/>
@@ -6396,7 +5936,7 @@
       <c r="H338" s="4"/>
       <c r="I338" s="4"/>
     </row>
-    <row r="339" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A339" s="4"/>
       <c r="B339" s="4"/>
       <c r="C339" s="4"/>
@@ -6407,7 +5947,7 @@
       <c r="H339" s="4"/>
       <c r="I339" s="4"/>
     </row>
-    <row r="340" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A340" s="4"/>
       <c r="B340" s="4"/>
       <c r="C340" s="4"/>
@@ -6418,7 +5958,7 @@
       <c r="H340" s="4"/>
       <c r="I340" s="4"/>
     </row>
-    <row r="341" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A341" s="4"/>
       <c r="B341" s="4"/>
       <c r="C341" s="4"/>
@@ -6429,7 +5969,7 @@
       <c r="H341" s="4"/>
       <c r="I341" s="4"/>
     </row>
-    <row r="342" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A342" s="4"/>
       <c r="B342" s="4"/>
       <c r="C342" s="4"/>
@@ -6440,7 +5980,7 @@
       <c r="H342" s="4"/>
       <c r="I342" s="4"/>
     </row>
-    <row r="343" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A343" s="4"/>
       <c r="B343" s="4"/>
       <c r="C343" s="4"/>
@@ -6451,7 +5991,7 @@
       <c r="H343" s="4"/>
       <c r="I343" s="4"/>
     </row>
-    <row r="344" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A344" s="4"/>
       <c r="B344" s="4"/>
       <c r="C344" s="4"/>
@@ -6462,7 +6002,7 @@
       <c r="H344" s="4"/>
       <c r="I344" s="4"/>
     </row>
-    <row r="345" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A345" s="4"/>
       <c r="B345" s="4"/>
       <c r="C345" s="4"/>
@@ -6473,7 +6013,7 @@
       <c r="H345" s="4"/>
       <c r="I345" s="4"/>
     </row>
-    <row r="346" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A346" s="4"/>
       <c r="B346" s="4"/>
       <c r="C346" s="4"/>
@@ -6484,7 +6024,7 @@
       <c r="H346" s="4"/>
       <c r="I346" s="4"/>
     </row>
-    <row r="347" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A347" s="4"/>
       <c r="B347" s="4"/>
       <c r="C347" s="4"/>
@@ -6495,7 +6035,7 @@
       <c r="H347" s="4"/>
       <c r="I347" s="4"/>
     </row>
-    <row r="348" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A348" s="4"/>
       <c r="B348" s="4"/>
       <c r="C348" s="4"/>
@@ -6506,7 +6046,7 @@
       <c r="H348" s="4"/>
       <c r="I348" s="4"/>
     </row>
-    <row r="349" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A349" s="4"/>
       <c r="B349" s="4"/>
       <c r="C349" s="4"/>
@@ -6517,7 +6057,7 @@
       <c r="H349" s="4"/>
       <c r="I349" s="4"/>
     </row>
-    <row r="350" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A350" s="4"/>
       <c r="B350" s="4"/>
       <c r="C350" s="4"/>
@@ -6528,7 +6068,7 @@
       <c r="H350" s="4"/>
       <c r="I350" s="4"/>
     </row>
-    <row r="351" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A351" s="4"/>
       <c r="B351" s="4"/>
       <c r="C351" s="4"/>
@@ -6539,7 +6079,7 @@
       <c r="H351" s="4"/>
       <c r="I351" s="4"/>
     </row>
-    <row r="352" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A352" s="4"/>
       <c r="B352" s="4"/>
       <c r="C352" s="4"/>
@@ -6550,7 +6090,7 @@
       <c r="H352" s="4"/>
       <c r="I352" s="4"/>
     </row>
-    <row r="353" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A353" s="4"/>
       <c r="B353" s="4"/>
       <c r="C353" s="4"/>
@@ -6561,7 +6101,7 @@
       <c r="H353" s="4"/>
       <c r="I353" s="4"/>
     </row>
-    <row r="354" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A354" s="4"/>
       <c r="B354" s="4"/>
       <c r="C354" s="4"/>
@@ -6572,7 +6112,7 @@
       <c r="H354" s="4"/>
       <c r="I354" s="4"/>
     </row>
-    <row r="355" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A355" s="4"/>
       <c r="B355" s="4"/>
       <c r="C355" s="4"/>
@@ -6583,7 +6123,7 @@
       <c r="H355" s="4"/>
       <c r="I355" s="4"/>
     </row>
-    <row r="356" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A356" s="4"/>
       <c r="B356" s="4"/>
       <c r="C356" s="4"/>
@@ -6594,7 +6134,7 @@
       <c r="H356" s="4"/>
       <c r="I356" s="4"/>
     </row>
-    <row r="357" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A357" s="4"/>
       <c r="B357" s="4"/>
       <c r="C357" s="4"/>
@@ -6605,7 +6145,7 @@
       <c r="H357" s="4"/>
       <c r="I357" s="4"/>
     </row>
-    <row r="358" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A358" s="4"/>
       <c r="B358" s="4"/>
       <c r="C358" s="4"/>
@@ -6616,7 +6156,7 @@
       <c r="H358" s="4"/>
       <c r="I358" s="4"/>
     </row>
-    <row r="359" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A359" s="4"/>
       <c r="B359" s="4"/>
       <c r="C359" s="4"/>
@@ -6627,7 +6167,7 @@
       <c r="H359" s="4"/>
       <c r="I359" s="4"/>
     </row>
-    <row r="360" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A360" s="4"/>
       <c r="B360" s="4"/>
       <c r="C360" s="4"/>
@@ -6638,7 +6178,7 @@
       <c r="H360" s="4"/>
       <c r="I360" s="4"/>
     </row>
-    <row r="361" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A361" s="4"/>
       <c r="B361" s="4"/>
       <c r="C361" s="4"/>
@@ -6649,7 +6189,7 @@
       <c r="H361" s="4"/>
       <c r="I361" s="4"/>
     </row>
-    <row r="362" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A362" s="4"/>
       <c r="B362" s="4"/>
       <c r="C362" s="4"/>
@@ -6660,7 +6200,7 @@
       <c r="H362" s="4"/>
       <c r="I362" s="4"/>
     </row>
-    <row r="363" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A363" s="4"/>
       <c r="B363" s="4"/>
       <c r="C363" s="4"/>
@@ -6671,7 +6211,7 @@
       <c r="H363" s="4"/>
       <c r="I363" s="4"/>
     </row>
-    <row r="364" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A364" s="4"/>
       <c r="B364" s="4"/>
       <c r="C364" s="4"/>
@@ -6682,7 +6222,7 @@
       <c r="H364" s="4"/>
       <c r="I364" s="4"/>
     </row>
-    <row r="365" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A365" s="4"/>
       <c r="B365" s="4"/>
       <c r="C365" s="4"/>
@@ -6693,7 +6233,7 @@
       <c r="H365" s="4"/>
       <c r="I365" s="4"/>
     </row>
-    <row r="366" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A366" s="4"/>
       <c r="B366" s="4"/>
       <c r="C366" s="4"/>
@@ -6704,7 +6244,7 @@
       <c r="H366" s="4"/>
       <c r="I366" s="4"/>
     </row>
-    <row r="367" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A367" s="4"/>
       <c r="B367" s="4"/>
       <c r="C367" s="4"/>
@@ -6715,7 +6255,7 @@
       <c r="H367" s="4"/>
       <c r="I367" s="4"/>
     </row>
-    <row r="368" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A368" s="4"/>
       <c r="B368" s="4"/>
       <c r="C368" s="4"/>
@@ -6726,7 +6266,7 @@
       <c r="H368" s="4"/>
       <c r="I368" s="4"/>
     </row>
-    <row r="369" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A369" s="4"/>
       <c r="B369" s="4"/>
       <c r="C369" s="4"/>
@@ -6737,7 +6277,7 @@
       <c r="H369" s="4"/>
       <c r="I369" s="4"/>
     </row>
-    <row r="370" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A370" s="4"/>
       <c r="B370" s="4"/>
       <c r="C370" s="4"/>
@@ -6748,7 +6288,7 @@
       <c r="H370" s="4"/>
       <c r="I370" s="4"/>
     </row>
-    <row r="371" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A371" s="4"/>
       <c r="B371" s="4"/>
       <c r="C371" s="4"/>
@@ -6759,7 +6299,7 @@
       <c r="H371" s="4"/>
       <c r="I371" s="4"/>
     </row>
-    <row r="372" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A372" s="4"/>
       <c r="B372" s="4"/>
       <c r="C372" s="4"/>
@@ -6770,7 +6310,7 @@
       <c r="H372" s="4"/>
       <c r="I372" s="4"/>
     </row>
-    <row r="373" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A373" s="4"/>
       <c r="B373" s="4"/>
       <c r="C373" s="4"/>
@@ -6781,7 +6321,7 @@
       <c r="H373" s="4"/>
       <c r="I373" s="4"/>
     </row>
-    <row r="374" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A374" s="4"/>
       <c r="B374" s="4"/>
       <c r="C374" s="4"/>
@@ -6792,7 +6332,7 @@
       <c r="H374" s="4"/>
       <c r="I374" s="4"/>
     </row>
-    <row r="375" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A375" s="4"/>
       <c r="B375" s="4"/>
       <c r="C375" s="4"/>
@@ -6803,7 +6343,7 @@
       <c r="H375" s="4"/>
       <c r="I375" s="4"/>
     </row>
-    <row r="376" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A376" s="4"/>
       <c r="B376" s="4"/>
       <c r="C376" s="4"/>
@@ -6814,7 +6354,7 @@
       <c r="H376" s="4"/>
       <c r="I376" s="4"/>
     </row>
-    <row r="377" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A377" s="4"/>
       <c r="B377" s="4"/>
       <c r="C377" s="4"/>
@@ -6825,7 +6365,7 @@
       <c r="H377" s="4"/>
       <c r="I377" s="4"/>
     </row>
-    <row r="378" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A378" s="4"/>
       <c r="B378" s="4"/>
       <c r="C378" s="4"/>
@@ -6836,7 +6376,7 @@
       <c r="H378" s="4"/>
       <c r="I378" s="4"/>
     </row>
-    <row r="379" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A379" s="4"/>
       <c r="B379" s="4"/>
       <c r="C379" s="4"/>
@@ -6847,7 +6387,7 @@
       <c r="H379" s="4"/>
       <c r="I379" s="4"/>
     </row>
-    <row r="380" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A380" s="4"/>
       <c r="B380" s="4"/>
       <c r="C380" s="4"/>
@@ -6858,7 +6398,7 @@
       <c r="H380" s="4"/>
       <c r="I380" s="4"/>
     </row>
-    <row r="381" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A381" s="4"/>
       <c r="B381" s="4"/>
       <c r="C381" s="4"/>
@@ -6869,7 +6409,7 @@
       <c r="H381" s="4"/>
       <c r="I381" s="4"/>
     </row>
-    <row r="382" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A382" s="4"/>
       <c r="B382" s="4"/>
       <c r="C382" s="4"/>
@@ -6880,7 +6420,7 @@
       <c r="H382" s="4"/>
       <c r="I382" s="4"/>
     </row>
-    <row r="383" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A383" s="4"/>
       <c r="B383" s="4"/>
       <c r="C383" s="4"/>
@@ -6891,7 +6431,7 @@
       <c r="H383" s="4"/>
       <c r="I383" s="4"/>
     </row>
-    <row r="384" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A384" s="4"/>
       <c r="B384" s="4"/>
       <c r="C384" s="4"/>
@@ -6902,7 +6442,7 @@
       <c r="H384" s="4"/>
       <c r="I384" s="4"/>
     </row>
-    <row r="385" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A385" s="4"/>
       <c r="B385" s="4"/>
       <c r="C385" s="4"/>
@@ -6913,7 +6453,7 @@
       <c r="H385" s="4"/>
       <c r="I385" s="4"/>
     </row>
-    <row r="386" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A386" s="4"/>
       <c r="B386" s="4"/>
       <c r="C386" s="4"/>
@@ -6924,7 +6464,7 @@
       <c r="H386" s="4"/>
       <c r="I386" s="4"/>
     </row>
-    <row r="387" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A387" s="4"/>
       <c r="B387" s="4"/>
       <c r="C387" s="4"/>
@@ -6935,7 +6475,7 @@
       <c r="H387" s="4"/>
       <c r="I387" s="4"/>
     </row>
-    <row r="388" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A388" s="4"/>
       <c r="B388" s="4"/>
       <c r="C388" s="4"/>
@@ -6946,7 +6486,7 @@
       <c r="H388" s="4"/>
       <c r="I388" s="4"/>
     </row>
-    <row r="389" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A389" s="4"/>
       <c r="B389" s="4"/>
       <c r="C389" s="4"/>
@@ -6957,7 +6497,7 @@
       <c r="H389" s="4"/>
       <c r="I389" s="4"/>
     </row>
-    <row r="390" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A390" s="4"/>
       <c r="B390" s="4"/>
       <c r="C390" s="4"/>
@@ -6968,7 +6508,7 @@
       <c r="H390" s="4"/>
       <c r="I390" s="4"/>
     </row>
-    <row r="391" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A391" s="4"/>
       <c r="B391" s="4"/>
       <c r="C391" s="4"/>
@@ -6979,7 +6519,7 @@
       <c r="H391" s="4"/>
       <c r="I391" s="4"/>
     </row>
-    <row r="392" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A392" s="4"/>
       <c r="B392" s="4"/>
       <c r="C392" s="4"/>
@@ -6990,7 +6530,7 @@
       <c r="H392" s="4"/>
       <c r="I392" s="4"/>
     </row>
-    <row r="393" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A393" s="4"/>
       <c r="B393" s="4"/>
       <c r="C393" s="4"/>
@@ -7001,7 +6541,7 @@
       <c r="H393" s="4"/>
       <c r="I393" s="4"/>
     </row>
-    <row r="394" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A394" s="4"/>
       <c r="B394" s="4"/>
       <c r="C394" s="4"/>
@@ -7012,7 +6552,7 @@
       <c r="H394" s="4"/>
       <c r="I394" s="4"/>
     </row>
-    <row r="395" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A395" s="4"/>
       <c r="B395" s="4"/>
       <c r="C395" s="4"/>
@@ -7023,7 +6563,7 @@
       <c r="H395" s="4"/>
       <c r="I395" s="4"/>
     </row>
-    <row r="396" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A396" s="4"/>
       <c r="B396" s="4"/>
       <c r="C396" s="4"/>
@@ -7034,7 +6574,7 @@
       <c r="H396" s="4"/>
       <c r="I396" s="4"/>
     </row>
-    <row r="397" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A397" s="4"/>
       <c r="B397" s="4"/>
       <c r="C397" s="4"/>
@@ -7045,7 +6585,7 @@
       <c r="H397" s="4"/>
       <c r="I397" s="4"/>
     </row>
-    <row r="398" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A398" s="4"/>
       <c r="B398" s="4"/>
       <c r="C398" s="4"/>
@@ -7056,7 +6596,7 @@
       <c r="H398" s="4"/>
       <c r="I398" s="4"/>
     </row>
-    <row r="399" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A399" s="4"/>
       <c r="B399" s="4"/>
       <c r="C399" s="4"/>
@@ -7067,7 +6607,7 @@
       <c r="H399" s="4"/>
       <c r="I399" s="4"/>
     </row>
-    <row r="400" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A400" s="4"/>
       <c r="B400" s="4"/>
       <c r="C400" s="4"/>
@@ -7078,7 +6618,7 @@
       <c r="H400" s="4"/>
       <c r="I400" s="4"/>
     </row>
-    <row r="401" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A401" s="4"/>
       <c r="B401" s="4"/>
       <c r="C401" s="4"/>
@@ -7089,7 +6629,7 @@
       <c r="H401" s="4"/>
       <c r="I401" s="4"/>
     </row>
-    <row r="402" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A402" s="4"/>
       <c r="B402" s="4"/>
       <c r="C402" s="4"/>
@@ -7100,7 +6640,7 @@
       <c r="H402" s="4"/>
       <c r="I402" s="4"/>
     </row>
-    <row r="403" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A403" s="4"/>
       <c r="B403" s="4"/>
       <c r="C403" s="4"/>
@@ -7111,7 +6651,7 @@
       <c r="H403" s="4"/>
       <c r="I403" s="4"/>
     </row>
-    <row r="404" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A404" s="4"/>
       <c r="B404" s="4"/>
       <c r="C404" s="4"/>
@@ -7122,7 +6662,7 @@
       <c r="H404" s="4"/>
       <c r="I404" s="4"/>
     </row>
-    <row r="405" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A405" s="4"/>
       <c r="B405" s="4"/>
       <c r="C405" s="4"/>
@@ -7133,7 +6673,7 @@
       <c r="H405" s="4"/>
       <c r="I405" s="4"/>
     </row>
-    <row r="406" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A406" s="4"/>
       <c r="B406" s="4"/>
       <c r="C406" s="4"/>
@@ -7144,7 +6684,7 @@
       <c r="H406" s="4"/>
       <c r="I406" s="4"/>
     </row>
-    <row r="407" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A407" s="4"/>
       <c r="B407" s="4"/>
       <c r="C407" s="4"/>
@@ -7155,7 +6695,7 @@
       <c r="H407" s="4"/>
       <c r="I407" s="4"/>
     </row>
-    <row r="408" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A408" s="4"/>
       <c r="B408" s="4"/>
       <c r="C408" s="4"/>
@@ -7166,7 +6706,7 @@
       <c r="H408" s="4"/>
       <c r="I408" s="4"/>
     </row>
-    <row r="409" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A409" s="4"/>
       <c r="B409" s="4"/>
       <c r="C409" s="4"/>
@@ -7177,7 +6717,7 @@
       <c r="H409" s="4"/>
       <c r="I409" s="4"/>
     </row>
-    <row r="410" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A410" s="4"/>
       <c r="B410" s="4"/>
       <c r="C410" s="4"/>
@@ -7188,7 +6728,7 @@
       <c r="H410" s="4"/>
       <c r="I410" s="4"/>
     </row>
-    <row r="411" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A411" s="4"/>
       <c r="B411" s="4"/>
       <c r="C411" s="4"/>
@@ -7199,7 +6739,7 @@
       <c r="H411" s="4"/>
       <c r="I411" s="4"/>
     </row>
-    <row r="412" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A412" s="4"/>
       <c r="B412" s="4"/>
       <c r="C412" s="4"/>
@@ -7210,7 +6750,7 @@
       <c r="H412" s="4"/>
       <c r="I412" s="4"/>
     </row>
-    <row r="413" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A413" s="4"/>
       <c r="B413" s="4"/>
       <c r="C413" s="4"/>
@@ -7221,7 +6761,7 @@
       <c r="H413" s="4"/>
       <c r="I413" s="4"/>
     </row>
-    <row r="414" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A414" s="4"/>
       <c r="B414" s="4"/>
       <c r="C414" s="4"/>
@@ -7232,7 +6772,7 @@
       <c r="H414" s="4"/>
       <c r="I414" s="4"/>
     </row>
-    <row r="415" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A415" s="4"/>
       <c r="B415" s="4"/>
       <c r="C415" s="4"/>
@@ -7243,7 +6783,7 @@
       <c r="H415" s="4"/>
       <c r="I415" s="4"/>
     </row>
-    <row r="416" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A416" s="4"/>
       <c r="B416" s="4"/>
       <c r="C416" s="4"/>
@@ -7254,7 +6794,7 @@
       <c r="H416" s="4"/>
       <c r="I416" s="4"/>
     </row>
-    <row r="417" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A417" s="4"/>
       <c r="B417" s="4"/>
       <c r="C417" s="4"/>
@@ -7265,7 +6805,7 @@
       <c r="H417" s="4"/>
       <c r="I417" s="4"/>
     </row>
-    <row r="418" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A418" s="4"/>
       <c r="B418" s="4"/>
       <c r="C418" s="4"/>
@@ -7276,7 +6816,7 @@
       <c r="H418" s="4"/>
       <c r="I418" s="4"/>
     </row>
-    <row r="419" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A419" s="4"/>
       <c r="B419" s="4"/>
       <c r="C419" s="4"/>
@@ -7287,7 +6827,7 @@
       <c r="H419" s="4"/>
       <c r="I419" s="4"/>
     </row>
-    <row r="420" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A420" s="4"/>
       <c r="B420" s="4"/>
       <c r="C420" s="4"/>
@@ -7298,7 +6838,7 @@
       <c r="H420" s="4"/>
       <c r="I420" s="4"/>
     </row>
-    <row r="421" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A421" s="4"/>
       <c r="B421" s="4"/>
       <c r="C421" s="4"/>
@@ -7309,7 +6849,7 @@
       <c r="H421" s="4"/>
       <c r="I421" s="4"/>
     </row>
-    <row r="422" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A422" s="4"/>
       <c r="B422" s="4"/>
       <c r="C422" s="4"/>
@@ -7320,7 +6860,7 @@
       <c r="H422" s="4"/>
       <c r="I422" s="4"/>
     </row>
-    <row r="423" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A423" s="4"/>
       <c r="B423" s="4"/>
       <c r="C423" s="4"/>
@@ -7331,7 +6871,7 @@
       <c r="H423" s="4"/>
       <c r="I423" s="4"/>
     </row>
-    <row r="424" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A424" s="4"/>
       <c r="B424" s="4"/>
       <c r="C424" s="4"/>
@@ -7342,7 +6882,7 @@
       <c r="H424" s="4"/>
       <c r="I424" s="4"/>
     </row>
-    <row r="425" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A425" s="4"/>
       <c r="B425" s="4"/>
       <c r="C425" s="4"/>
@@ -7353,7 +6893,7 @@
       <c r="H425" s="4"/>
       <c r="I425" s="4"/>
     </row>
-    <row r="426" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A426" s="4"/>
       <c r="B426" s="4"/>
       <c r="C426" s="4"/>
@@ -7364,7 +6904,7 @@
       <c r="H426" s="4"/>
       <c r="I426" s="4"/>
     </row>
-    <row r="427" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A427" s="4"/>
       <c r="B427" s="4"/>
       <c r="C427" s="4"/>
@@ -7375,7 +6915,7 @@
       <c r="H427" s="4"/>
       <c r="I427" s="4"/>
     </row>
-    <row r="428" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A428" s="4"/>
       <c r="B428" s="4"/>
       <c r="C428" s="4"/>
@@ -7386,7 +6926,7 @@
       <c r="H428" s="4"/>
       <c r="I428" s="4"/>
     </row>
-    <row r="429" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A429" s="4"/>
       <c r="B429" s="4"/>
       <c r="C429" s="4"/>
@@ -7397,7 +6937,7 @@
       <c r="H429" s="4"/>
       <c r="I429" s="4"/>
     </row>
-    <row r="430" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A430" s="4"/>
       <c r="B430" s="4"/>
       <c r="C430" s="4"/>
@@ -7408,7 +6948,7 @@
       <c r="H430" s="4"/>
       <c r="I430" s="4"/>
     </row>
-    <row r="431" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A431" s="4"/>
       <c r="B431" s="4"/>
       <c r="C431" s="4"/>
@@ -7419,7 +6959,7 @@
       <c r="H431" s="4"/>
       <c r="I431" s="4"/>
     </row>
-    <row r="432" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A432" s="4"/>
       <c r="B432" s="4"/>
       <c r="C432" s="4"/>
@@ -7430,7 +6970,7 @@
       <c r="H432" s="4"/>
       <c r="I432" s="4"/>
     </row>
-    <row r="433" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A433" s="4"/>
       <c r="B433" s="4"/>
       <c r="C433" s="4"/>
@@ -7441,7 +6981,7 @@
       <c r="H433" s="4"/>
       <c r="I433" s="4"/>
     </row>
-    <row r="434" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A434" s="4"/>
       <c r="B434" s="4"/>
       <c r="C434" s="4"/>
@@ -7452,7 +6992,7 @@
       <c r="H434" s="4"/>
       <c r="I434" s="4"/>
     </row>
-    <row r="435" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A435" s="4"/>
       <c r="B435" s="4"/>
       <c r="C435" s="4"/>
@@ -7463,7 +7003,7 @@
       <c r="H435" s="4"/>
       <c r="I435" s="4"/>
     </row>
-    <row r="436" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A436" s="4"/>
       <c r="B436" s="4"/>
       <c r="C436" s="4"/>
@@ -7474,7 +7014,7 @@
       <c r="H436" s="4"/>
       <c r="I436" s="4"/>
     </row>
-    <row r="437" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A437" s="4"/>
       <c r="B437" s="4"/>
       <c r="C437" s="4"/>
@@ -7485,7 +7025,7 @@
       <c r="H437" s="4"/>
       <c r="I437" s="4"/>
     </row>
-    <row r="438" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A438" s="4"/>
       <c r="B438" s="4"/>
       <c r="C438" s="4"/>
@@ -7496,7 +7036,7 @@
       <c r="H438" s="4"/>
       <c r="I438" s="4"/>
     </row>
-    <row r="439" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A439" s="4"/>
       <c r="B439" s="4"/>
       <c r="C439" s="4"/>
@@ -7507,7 +7047,7 @@
       <c r="H439" s="4"/>
       <c r="I439" s="4"/>
     </row>
-    <row r="440" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A440" s="4"/>
       <c r="B440" s="4"/>
       <c r="C440" s="4"/>
@@ -7518,7 +7058,7 @@
       <c r="H440" s="4"/>
       <c r="I440" s="4"/>
     </row>
-    <row r="441" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A441" s="4"/>
       <c r="B441" s="4"/>
       <c r="C441" s="4"/>
@@ -7529,7 +7069,7 @@
       <c r="H441" s="4"/>
       <c r="I441" s="4"/>
     </row>
-    <row r="442" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A442" s="4"/>
       <c r="B442" s="4"/>
       <c r="C442" s="4"/>
@@ -7540,7 +7080,7 @@
       <c r="H442" s="4"/>
       <c r="I442" s="4"/>
     </row>
-    <row r="443" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A443" s="4"/>
       <c r="B443" s="4"/>
       <c r="C443" s="4"/>
@@ -7551,7 +7091,7 @@
       <c r="H443" s="4"/>
       <c r="I443" s="4"/>
     </row>
-    <row r="444" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A444" s="4"/>
       <c r="B444" s="4"/>
       <c r="C444" s="4"/>
@@ -7562,7 +7102,7 @@
       <c r="H444" s="4"/>
       <c r="I444" s="4"/>
     </row>
-    <row r="445" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A445" s="4"/>
       <c r="B445" s="4"/>
       <c r="C445" s="4"/>
@@ -7573,7 +7113,7 @@
       <c r="H445" s="4"/>
       <c r="I445" s="4"/>
     </row>
-    <row r="446" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A446" s="4"/>
       <c r="B446" s="4"/>
       <c r="C446" s="4"/>
@@ -7584,7 +7124,7 @@
       <c r="H446" s="4"/>
       <c r="I446" s="4"/>
     </row>
-    <row r="447" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A447" s="4"/>
       <c r="B447" s="4"/>
       <c r="C447" s="4"/>
@@ -7595,7 +7135,7 @@
       <c r="H447" s="4"/>
       <c r="I447" s="4"/>
     </row>
-    <row r="448" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A448" s="4"/>
       <c r="B448" s="4"/>
       <c r="C448" s="4"/>
@@ -7606,7 +7146,7 @@
       <c r="H448" s="4"/>
       <c r="I448" s="4"/>
     </row>
-    <row r="449" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A449" s="4"/>
       <c r="B449" s="4"/>
       <c r="C449" s="4"/>
@@ -7617,7 +7157,7 @@
       <c r="H449" s="4"/>
       <c r="I449" s="4"/>
     </row>
-    <row r="450" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A450" s="4"/>
       <c r="B450" s="4"/>
       <c r="C450" s="4"/>
@@ -7628,7 +7168,7 @@
       <c r="H450" s="4"/>
       <c r="I450" s="4"/>
     </row>
-    <row r="451" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A451" s="4"/>
       <c r="B451" s="4"/>
       <c r="C451" s="4"/>
@@ -7639,7 +7179,7 @@
       <c r="H451" s="4"/>
       <c r="I451" s="4"/>
     </row>
-    <row r="452" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A452" s="4"/>
       <c r="B452" s="4"/>
       <c r="C452" s="4"/>
@@ -7650,7 +7190,7 @@
       <c r="H452" s="4"/>
       <c r="I452" s="4"/>
     </row>
-    <row r="453" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A453" s="4"/>
       <c r="B453" s="4"/>
       <c r="C453" s="4"/>
@@ -7661,7 +7201,7 @@
       <c r="H453" s="4"/>
       <c r="I453" s="4"/>
     </row>
-    <row r="454" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A454" s="4"/>
       <c r="B454" s="4"/>
       <c r="C454" s="4"/>
@@ -7672,7 +7212,7 @@
       <c r="H454" s="4"/>
       <c r="I454" s="4"/>
     </row>
-    <row r="455" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A455" s="4"/>
       <c r="B455" s="4"/>
       <c r="C455" s="4"/>
@@ -7683,7 +7223,7 @@
       <c r="H455" s="4"/>
       <c r="I455" s="4"/>
     </row>
-    <row r="456" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A456" s="4"/>
       <c r="B456" s="4"/>
       <c r="C456" s="4"/>
@@ -7694,7 +7234,7 @@
       <c r="H456" s="4"/>
       <c r="I456" s="4"/>
     </row>
-    <row r="457" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A457" s="4"/>
       <c r="B457" s="4"/>
       <c r="C457" s="4"/>
@@ -7705,7 +7245,7 @@
       <c r="H457" s="4"/>
       <c r="I457" s="4"/>
     </row>
-    <row r="458" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A458" s="4"/>
       <c r="B458" s="4"/>
       <c r="C458" s="4"/>
@@ -7716,7 +7256,7 @@
       <c r="H458" s="4"/>
       <c r="I458" s="4"/>
     </row>
-    <row r="459" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A459" s="4"/>
       <c r="B459" s="4"/>
       <c r="C459" s="4"/>
@@ -7727,7 +7267,7 @@
       <c r="H459" s="4"/>
       <c r="I459" s="4"/>
     </row>
-    <row r="460" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A460" s="4"/>
       <c r="B460" s="4"/>
       <c r="C460" s="4"/>
@@ -7738,7 +7278,7 @@
       <c r="H460" s="4"/>
       <c r="I460" s="4"/>
     </row>
-    <row r="461" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A461" s="4"/>
       <c r="B461" s="4"/>
       <c r="C461" s="4"/>
@@ -7749,7 +7289,7 @@
       <c r="H461" s="4"/>
       <c r="I461" s="4"/>
     </row>
-    <row r="462" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A462" s="4"/>
       <c r="B462" s="4"/>
       <c r="C462" s="4"/>
@@ -7760,7 +7300,7 @@
       <c r="H462" s="4"/>
       <c r="I462" s="4"/>
     </row>
-    <row r="463" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A463" s="4"/>
       <c r="B463" s="4"/>
       <c r="C463" s="4"/>
@@ -7771,7 +7311,7 @@
       <c r="H463" s="4"/>
       <c r="I463" s="4"/>
     </row>
-    <row r="464" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A464" s="4"/>
       <c r="B464" s="4"/>
       <c r="C464" s="4"/>
@@ -7782,7 +7322,7 @@
       <c r="H464" s="4"/>
       <c r="I464" s="4"/>
     </row>
-    <row r="465" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A465" s="4"/>
       <c r="B465" s="4"/>
       <c r="C465" s="4"/>
@@ -7793,7 +7333,7 @@
       <c r="H465" s="4"/>
       <c r="I465" s="4"/>
     </row>
-    <row r="466" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A466" s="4"/>
       <c r="B466" s="4"/>
       <c r="C466" s="4"/>
@@ -7804,7 +7344,7 @@
       <c r="H466" s="4"/>
       <c r="I466" s="4"/>
     </row>
-    <row r="467" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A467" s="4"/>
       <c r="B467" s="4"/>
       <c r="C467" s="4"/>
@@ -7815,7 +7355,7 @@
       <c r="H467" s="4"/>
       <c r="I467" s="4"/>
     </row>
-    <row r="468" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A468" s="4"/>
       <c r="B468" s="4"/>
       <c r="C468" s="4"/>
@@ -7826,7 +7366,7 @@
       <c r="H468" s="4"/>
       <c r="I468" s="4"/>
     </row>
-    <row r="469" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A469" s="4"/>
       <c r="B469" s="4"/>
       <c r="C469" s="4"/>
@@ -7837,7 +7377,7 @@
       <c r="H469" s="4"/>
       <c r="I469" s="4"/>
     </row>
-    <row r="470" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A470" s="4"/>
       <c r="B470" s="4"/>
       <c r="C470" s="4"/>
@@ -7848,7 +7388,7 @@
       <c r="H470" s="4"/>
       <c r="I470" s="4"/>
     </row>
-    <row r="471" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A471" s="4"/>
       <c r="B471" s="4"/>
       <c r="C471" s="4"/>
@@ -7859,7 +7399,7 @@
       <c r="H471" s="4"/>
       <c r="I471" s="4"/>
     </row>
-    <row r="472" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A472" s="4"/>
       <c r="B472" s="4"/>
       <c r="C472" s="4"/>
@@ -7870,7 +7410,7 @@
       <c r="H472" s="4"/>
       <c r="I472" s="4"/>
     </row>
-    <row r="473" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A473" s="4"/>
       <c r="B473" s="4"/>
       <c r="C473" s="4"/>
@@ -7881,7 +7421,7 @@
       <c r="H473" s="4"/>
       <c r="I473" s="4"/>
     </row>
-    <row r="474" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A474" s="4"/>
       <c r="B474" s="4"/>
       <c r="C474" s="4"/>
@@ -7892,7 +7432,7 @@
       <c r="H474" s="4"/>
       <c r="I474" s="4"/>
     </row>
-    <row r="475" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A475" s="4"/>
       <c r="B475" s="4"/>
       <c r="C475" s="4"/>
@@ -7903,7 +7443,7 @@
       <c r="H475" s="4"/>
       <c r="I475" s="4"/>
     </row>
-    <row r="476" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A476" s="4"/>
       <c r="B476" s="4"/>
       <c r="C476" s="4"/>
@@ -7914,7 +7454,7 @@
       <c r="H476" s="4"/>
       <c r="I476" s="4"/>
     </row>
-    <row r="477" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A477" s="4"/>
       <c r="B477" s="4"/>
       <c r="C477" s="4"/>
@@ -7925,7 +7465,7 @@
       <c r="H477" s="4"/>
       <c r="I477" s="4"/>
     </row>
-    <row r="478" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A478" s="4"/>
       <c r="B478" s="4"/>
       <c r="C478" s="4"/>
@@ -7936,7 +7476,7 @@
       <c r="H478" s="4"/>
       <c r="I478" s="4"/>
     </row>
-    <row r="479" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A479" s="4"/>
       <c r="B479" s="4"/>
       <c r="C479" s="4"/>
@@ -7947,7 +7487,7 @@
       <c r="H479" s="4"/>
       <c r="I479" s="4"/>
     </row>
-    <row r="480" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A480" s="4"/>
       <c r="B480" s="4"/>
       <c r="C480" s="4"/>
@@ -7958,7 +7498,7 @@
       <c r="H480" s="4"/>
       <c r="I480" s="4"/>
     </row>
-    <row r="481" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A481" s="4"/>
       <c r="B481" s="4"/>
       <c r="C481" s="4"/>
@@ -7969,7 +7509,7 @@
       <c r="H481" s="4"/>
       <c r="I481" s="4"/>
     </row>
-    <row r="482" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A482" s="4"/>
       <c r="B482" s="4"/>
       <c r="C482" s="4"/>
@@ -7980,7 +7520,7 @@
       <c r="H482" s="4"/>
       <c r="I482" s="4"/>
     </row>
-    <row r="483" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A483" s="4"/>
       <c r="B483" s="4"/>
       <c r="C483" s="4"/>
@@ -7991,7 +7531,7 @@
       <c r="H483" s="4"/>
       <c r="I483" s="4"/>
     </row>
-    <row r="484" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A484" s="4"/>
       <c r="B484" s="4"/>
       <c r="C484" s="4"/>
@@ -8002,7 +7542,7 @@
       <c r="H484" s="4"/>
       <c r="I484" s="4"/>
     </row>
-    <row r="485" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A485" s="4"/>
       <c r="B485" s="4"/>
       <c r="C485" s="4"/>
@@ -8013,7 +7553,7 @@
       <c r="H485" s="4"/>
       <c r="I485" s="4"/>
     </row>
-    <row r="486" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A486" s="4"/>
       <c r="B486" s="4"/>
       <c r="C486" s="4"/>
@@ -8024,7 +7564,7 @@
       <c r="H486" s="4"/>
       <c r="I486" s="4"/>
     </row>
-    <row r="487" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A487" s="4"/>
       <c r="B487" s="4"/>
       <c r="C487" s="4"/>
@@ -8035,7 +7575,7 @@
       <c r="H487" s="4"/>
       <c r="I487" s="4"/>
     </row>
-    <row r="488" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A488" s="4"/>
       <c r="B488" s="4"/>
       <c r="C488" s="4"/>
@@ -8046,7 +7586,7 @@
       <c r="H488" s="4"/>
       <c r="I488" s="4"/>
     </row>
-    <row r="489" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A489" s="4"/>
       <c r="B489" s="4"/>
       <c r="C489" s="4"/>
@@ -8057,7 +7597,7 @@
       <c r="H489" s="4"/>
       <c r="I489" s="4"/>
     </row>
-    <row r="490" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A490" s="4"/>
       <c r="B490" s="4"/>
       <c r="C490" s="4"/>
@@ -8068,7 +7608,7 @@
       <c r="H490" s="4"/>
       <c r="I490" s="4"/>
     </row>
-    <row r="491" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A491" s="4"/>
       <c r="B491" s="4"/>
       <c r="C491" s="4"/>
@@ -8079,7 +7619,7 @@
       <c r="H491" s="4"/>
       <c r="I491" s="4"/>
     </row>
-    <row r="492" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A492" s="4"/>
       <c r="B492" s="4"/>
       <c r="C492" s="4"/>
@@ -8090,7 +7630,7 @@
       <c r="H492" s="4"/>
       <c r="I492" s="4"/>
     </row>
-    <row r="493" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A493" s="4"/>
       <c r="B493" s="4"/>
       <c r="C493" s="4"/>
@@ -8101,7 +7641,7 @@
       <c r="H493" s="4"/>
       <c r="I493" s="4"/>
     </row>
-    <row r="494" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A494" s="4"/>
       <c r="B494" s="4"/>
       <c r="C494" s="4"/>
@@ -8112,7 +7652,7 @@
       <c r="H494" s="4"/>
       <c r="I494" s="4"/>
     </row>
-    <row r="495" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A495" s="4"/>
       <c r="B495" s="4"/>
       <c r="C495" s="4"/>
@@ -8123,7 +7663,7 @@
       <c r="H495" s="4"/>
       <c r="I495" s="4"/>
     </row>
-    <row r="496" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A496" s="4"/>
       <c r="B496" s="4"/>
       <c r="C496" s="4"/>
@@ -8134,7 +7674,7 @@
       <c r="H496" s="4"/>
       <c r="I496" s="4"/>
     </row>
-    <row r="497" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A497" s="4"/>
       <c r="B497" s="4"/>
       <c r="C497" s="4"/>
@@ -8145,7 +7685,7 @@
       <c r="H497" s="4"/>
       <c r="I497" s="4"/>
     </row>
-    <row r="498" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A498" s="4"/>
       <c r="B498" s="4"/>
       <c r="C498" s="4"/>
@@ -8156,7 +7696,7 @@
       <c r="H498" s="4"/>
       <c r="I498" s="4"/>
     </row>
-    <row r="499" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A499" s="4"/>
       <c r="B499" s="4"/>
       <c r="C499" s="4"/>
@@ -8167,7 +7707,7 @@
       <c r="H499" s="4"/>
       <c r="I499" s="4"/>
     </row>
-    <row r="500" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A500" s="4"/>
       <c r="B500" s="4"/>
       <c r="C500" s="4"/>
@@ -8207,51 +7747,51 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:F7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5546875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="30.109375" style="10" customWidth="1"/>
-    <col min="2" max="6" width="25.109375" style="10" customWidth="1"/>
+    <col min="1" max="1" width="30.140625" style="6" customWidth="1"/>
+    <col min="2" max="6" width="25.140625" style="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+    <row r="1" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+    </row>
+    <row r="2" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-    </row>
-    <row r="2" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="22.8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:6" ht="24" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -8259,9 +7799,9 @@
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
     </row>
-    <row r="4" spans="1:6" ht="22.8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="24" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -8269,9 +7809,9 @@
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
     </row>
-    <row r="5" spans="1:6" ht="22.8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="24" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -8279,9 +7819,9 @@
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" spans="1:6" ht="22.8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="24" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -8289,9 +7829,9 @@
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
     </row>
-    <row r="7" spans="1:6" ht="22.8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="24" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
@@ -8312,62 +7852,62 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:E3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5546875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="34" style="10" customWidth="1"/>
-    <col min="2" max="2" width="15.44140625" style="10" customWidth="1"/>
-    <col min="3" max="3" width="28.88671875" style="10" customWidth="1"/>
-    <col min="4" max="4" width="56" style="10" customWidth="1"/>
-    <col min="5" max="5" width="26.33203125" style="10" customWidth="1"/>
+    <col min="1" max="1" width="34" style="6" customWidth="1"/>
+    <col min="2" max="2" width="15.42578125" style="6" customWidth="1"/>
+    <col min="3" max="3" width="28.85546875" style="6" customWidth="1"/>
+    <col min="4" max="4" width="56" style="6" customWidth="1"/>
+    <col min="5" max="5" width="26.28515625" style="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+    <row r="1" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+    </row>
+    <row r="2" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-    </row>
-    <row r="2" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="E2" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="39.6" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="B3" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="C3" s="15" t="s">
-        <v>87</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>74</v>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A3" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -8381,32 +7921,32 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5546875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.5546875" style="10"/>
-    <col min="2" max="2" width="43.6640625" style="10" customWidth="1"/>
+    <col min="1" max="1" width="12.5703125" style="6"/>
+    <col min="2" max="2" width="43.7109375" style="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="B2" s="12" t="s">
-        <v>56</v>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
